--- a/dataset/DevEx_Metrics.xlsx
+++ b/dataset/DevEx_Metrics.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\metrics and parser\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08C51BA4-46C8-410D-BD8C-354A882F6447}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE71621-B85A-4D55-81B5-B84F70F7D653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="29010" windowHeight="23385" tabRatio="506" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="metrics" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2044" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="855">
   <si>
     <t>id</t>
   </si>
@@ -1211,9 +1211,6 @@
     <t>Meyer et al. (2014)</t>
   </si>
   <si>
-    <t>5; 160; 501; 19; 39</t>
-  </si>
-  <si>
     <t>Meyer et al. (2017)</t>
   </si>
   <si>
@@ -1791,9 +1788,6 @@
     <t>511b; 511l; 516c</t>
   </si>
   <si>
-    <t>504; 11; 96; 214; 513; 517b</t>
-  </si>
-  <si>
     <t>CapitalOne</t>
   </si>
   <si>
@@ -1992,9 +1986,6 @@
     <t>501k; 131e; 199; 232a; 232</t>
   </si>
   <si>
-    <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 513</t>
-  </si>
-  <si>
     <t>232a; 232</t>
   </si>
   <si>
@@ -2556,9 +2547,6 @@
     <t>503; 501; 183; 522</t>
   </si>
   <si>
-    <t>514; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512; 520; 522</t>
-  </si>
-  <si>
     <t>501; 183; 522</t>
   </si>
   <si>
@@ -2602,6 +2590,27 @@
   </si>
   <si>
     <t>https://www.researchgate.net/profile/Charles-James-16/publication/385353040_Assessing_Developer_Productivity_and_Error_Reduction_with_TDD_and_BDD_Metrics/links/67218c1277f274616d50507b/Assessing-Developer-Productivity-and-Error-Reduction-with-TDD-and-BDD-Metrics.pdf</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3847122</t>
+  </si>
+  <si>
+    <t>523</t>
+  </si>
+  <si>
+    <t>Brandebusemeyer (2026)</t>
+  </si>
+  <si>
+    <t>504; 11; 96; 214; 513; 517b; 523</t>
+  </si>
+  <si>
+    <t>5; 160; 501; 19; 39; 523</t>
+  </si>
+  <si>
+    <t>514; 506;  503; 43; 96; 202; 235; 5; 6; 160; 501; 131; 183; 146; 512; 520; 522; 523</t>
+  </si>
+  <si>
+    <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 513; 523</t>
   </si>
 </sst>
 </file>
@@ -2699,7 +2708,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2780,11 +2789,6 @@
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -2798,6 +2802,16 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -2863,16 +2877,6 @@
     </dxf>
     <dxf>
       <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
@@ -2913,21 +2917,21 @@
     </dxf>
     <dxf>
       <font>
+        <color rgb="FF006100"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFC6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF9C5700"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFFFEB9C"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -3527,7 +3531,7 @@
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3554,16 +3558,16 @@
         <v>369</v>
       </c>
       <c r="P1" s="15" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -3577,16 +3581,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3619,16 +3623,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -3651,7 +3655,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3684,13 +3688,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>9</v>
@@ -3701,22 +3705,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="E4" s="13" t="s">
         <v>382</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3749,16 +3753,16 @@
         <v>4</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R4" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -3766,7 +3770,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
@@ -3775,13 +3779,13 @@
         <v>300</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>368</v>
@@ -3814,13 +3818,13 @@
         <v>5</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R5" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>9</v>
@@ -3846,7 +3850,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3879,13 +3883,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R6" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>9</v>
@@ -3899,19 +3903,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
@@ -3947,13 +3951,13 @@
         <v>93</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R7" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -3967,16 +3971,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -4009,13 +4013,13 @@
         <v>2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>9</v>
@@ -4032,16 +4036,16 @@
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -4074,13 +4078,13 @@
         <v>4</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R9" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>9</v>
@@ -4091,22 +4095,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>608</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>607</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>684</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>609</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>687</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>612</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -4139,13 +4143,13 @@
         <v>5</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R10" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>9</v>
@@ -4162,7 +4166,7 @@
         <v>9</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="E11" s="13" t="s">
         <v>306</v>
@@ -4171,7 +4175,7 @@
         <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -4204,13 +4208,13 @@
         <v>5</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R11" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>9</v>
@@ -4221,22 +4225,22 @@
         <v>17</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>42</v>
@@ -4246,7 +4250,7 @@
         <v>206</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="K12" s="3">
         <f>VLOOKUP(J12,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4269,13 +4273,13 @@
         <v>11</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R12" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>9</v>
@@ -4289,19 +4293,19 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D13" s="12" t="s">
         <v>473</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>474</v>
-      </c>
       <c r="E13" s="13" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -4337,10 +4341,10 @@
         <v>93</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R13" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S13" s="12" t="s">
         <v>9</v>
@@ -4354,19 +4358,19 @@
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>46</v>
@@ -4376,7 +4380,7 @@
         <v>207</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K14" s="3">
         <f>VLOOKUP(J14,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4399,13 +4403,13 @@
         <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R14" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>9</v>
@@ -4416,7 +4420,7 @@
         <v>20</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="C15" s="4" t="s">
         <v>162</v>
@@ -4425,13 +4429,13 @@
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>581</v>
+        <v>851</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>695</v>
+        <v>692</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>368</v>
@@ -4457,20 +4461,20 @@
       </c>
       <c r="N15" s="3">
         <f t="shared" si="1"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O15" s="3">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="P15" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R15" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S15" s="12" t="s">
         <v>9</v>
@@ -4481,7 +4485,7 @@
         <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>697</v>
+        <v>694</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
@@ -4496,7 +4500,7 @@
         <v>49</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4529,13 +4533,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R16" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>9</v>
@@ -4546,7 +4550,7 @@
         <v>23</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>163</v>
@@ -4558,10 +4562,10 @@
         <v>289</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>42</v>
@@ -4594,16 +4598,16 @@
         <v>2</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R17" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -4626,7 +4630,7 @@
         <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4659,13 +4663,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R18" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>9</v>
@@ -4676,10 +4680,10 @@
         <v>25</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
@@ -4691,7 +4695,7 @@
         <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>56</v>
@@ -4701,7 +4705,7 @@
         <v>208</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="K19" s="3">
         <f>VLOOKUP(J19,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4724,13 +4728,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R19" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S19" s="12" t="s">
         <v>9</v>
@@ -4741,7 +4745,7 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>9</v>
@@ -4753,10 +4757,10 @@
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>56</v>
@@ -4766,7 +4770,7 @@
         <v>208</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="K20" s="3">
         <f>VLOOKUP(J20,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4789,16 +4793,16 @@
         <v>3</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R20" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -4809,19 +4813,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4857,10 +4861,10 @@
         <v>93</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R21" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S21" s="12" t="s">
         <v>9</v>
@@ -4871,22 +4875,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
@@ -4919,13 +4923,13 @@
         <v>3</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R22" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S22" s="12" t="s">
         <v>9</v>
@@ -4942,16 +4946,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>56</v>
@@ -4987,13 +4991,13 @@
         <v>93</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R23" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -5004,19 +5008,19 @@
         <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F24" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
@@ -5049,16 +5053,16 @@
         <v>5</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R24" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -5066,7 +5070,7 @@
         <v>32</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
@@ -5081,7 +5085,7 @@
         <v>63</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>56</v>
@@ -5114,13 +5118,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R25" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S25" s="12" t="s">
         <v>9</v>
@@ -5146,7 +5150,7 @@
         <v>65</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -5179,13 +5183,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R26" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S26" s="12" t="s">
         <v>9</v>
@@ -5199,7 +5203,7 @@
         <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>377</v>
@@ -5208,10 +5212,10 @@
         <v>302</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5244,13 +5248,13 @@
         <v>6</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R27" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>9</v>
@@ -5264,19 +5268,19 @@
         <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>842</v>
+        <v>838</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>841</v>
+        <v>837</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>836</v>
+        <v>853</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>368</v>
@@ -5302,23 +5306,23 @@
       </c>
       <c r="N28" s="3">
         <f t="shared" si="1"/>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O28" s="3">
         <f t="shared" si="2"/>
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="P28" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R28" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="165" x14ac:dyDescent="0.25">
@@ -5326,7 +5330,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -5341,7 +5345,7 @@
         <v>72</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>10</v>
@@ -5374,13 +5378,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R29" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S29" s="12" t="s">
         <v>9</v>
@@ -5394,19 +5398,19 @@
         <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -5442,10 +5446,10 @@
         <v>93</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R30" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S30" s="12" t="s">
         <v>9</v>
@@ -5471,7 +5475,7 @@
         <v>75</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5504,13 +5508,13 @@
         <v>3</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S31" s="12" t="s">
         <v>9</v>
@@ -5530,13 +5534,13 @@
         <v>373</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H32" s="3" t="s">
         <v>368</v>
@@ -5572,10 +5576,10 @@
         <v>93</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R32" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S32" s="12" t="s">
         <v>9</v>
@@ -5601,7 +5605,7 @@
         <v>79</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>368</v>
@@ -5634,13 +5638,13 @@
         <v>6</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R33" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>9</v>
@@ -5654,19 +5658,19 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -5699,16 +5703,16 @@
         <v>3</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R34" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -5731,7 +5735,7 @@
         <v>83</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>368</v>
@@ -5764,13 +5768,13 @@
         <v>3</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R35" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>9</v>
@@ -5784,10 +5788,10 @@
         <v>85</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="E36" s="13" t="s">
         <v>378</v>
@@ -5796,7 +5800,7 @@
         <v>87</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
@@ -5832,10 +5836,10 @@
         <v>93</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R36" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S36" s="12" t="s">
         <v>9</v>
@@ -5855,13 +5859,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5894,13 +5898,13 @@
         <v>2</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R37" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S37" s="12" t="s">
         <v>9</v>
@@ -5911,10 +5915,10 @@
         <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>9</v>
@@ -5923,10 +5927,10 @@
         <v>316</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>42</v>
@@ -5962,10 +5966,10 @@
         <v>93</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R38" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S38" s="12" t="s">
         <v>9</v>
@@ -5976,22 +5980,22 @@
         <v>50</v>
       </c>
       <c r="B39" s="3" t="s">
+        <v>561</v>
+      </c>
+      <c r="C39" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="C39" s="4" t="s">
-        <v>563</v>
-      </c>
       <c r="D39" s="12" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="F39" s="4" t="s">
+        <v>520</v>
+      </c>
+      <c r="G39" s="3" t="s">
         <v>521</v>
-      </c>
-      <c r="G39" s="3" t="s">
-        <v>522</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>368</v>
@@ -6024,16 +6028,16 @@
         <v>13</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q39" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R39" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -6056,7 +6060,7 @@
         <v>94</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H40" s="3" t="s">
         <v>368</v>
@@ -6089,13 +6093,13 @@
         <v>4</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R40" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S40" s="12" t="s">
         <v>9</v>
@@ -6121,7 +6125,7 @@
         <v>96</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>10</v>
@@ -6154,13 +6158,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R41" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S41" s="12" t="s">
         <v>9</v>
@@ -6177,16 +6181,16 @@
         <v>164</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H42" s="3" t="s">
         <v>368</v>
@@ -6222,13 +6226,13 @@
         <v>93</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R42" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -6236,10 +6240,10 @@
         <v>59</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>9</v>
@@ -6251,7 +6255,7 @@
         <v>98</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H43" s="3" t="s">
         <v>368</v>
@@ -6287,13 +6291,13 @@
         <v>93</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R43" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -6301,22 +6305,22 @@
         <v>62</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6349,13 +6353,13 @@
         <v>14</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R44" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>9</v>
@@ -6372,7 +6376,7 @@
         <v>165</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E45" s="13" t="s">
         <v>313</v>
@@ -6381,7 +6385,7 @@
         <v>102</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -6417,10 +6421,10 @@
         <v>93</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R45" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>9</v>
@@ -6443,10 +6447,10 @@
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>21</v>
@@ -6479,13 +6483,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R46" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S46" s="12" t="s">
         <v>9</v>
@@ -6499,10 +6503,10 @@
         <v>104</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="E47" s="13" t="s">
         <v>379</v>
@@ -6511,7 +6515,7 @@
         <v>105</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
@@ -6544,13 +6548,13 @@
         <v>16</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R47" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S47" s="12" t="s">
         <v>9</v>
@@ -6561,7 +6565,7 @@
         <v>67</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>9</v>
@@ -6576,7 +6580,7 @@
         <v>106</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>42</v>
@@ -6609,13 +6613,13 @@
         <v>3</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R48" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S48" s="12" t="s">
         <v>9</v>
@@ -6629,7 +6633,7 @@
         <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D49" s="12" t="s">
         <v>293</v>
@@ -6641,7 +6645,7 @@
         <v>108</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>56</v>
@@ -6674,13 +6678,13 @@
         <v>3</v>
       </c>
       <c r="P49" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R49" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>9</v>
@@ -6694,19 +6698,19 @@
         <v>109</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
@@ -6739,16 +6743,16 @@
         <v>5</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R50" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -6756,7 +6760,7 @@
         <v>71</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>92</v>
@@ -6765,13 +6769,13 @@
         <v>300</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>15</v>
@@ -6804,13 +6808,13 @@
         <v>4</v>
       </c>
       <c r="P51" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R51" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>9</v>
@@ -6821,7 +6825,7 @@
         <v>72</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
@@ -6833,10 +6837,10 @@
         <v>302</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>10</v>
@@ -6869,16 +6873,16 @@
         <v>3</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R52" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -6901,7 +6905,7 @@
         <v>112</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>21</v>
@@ -6934,13 +6938,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R53" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S53" s="12" t="s">
         <v>9</v>
@@ -6951,10 +6955,10 @@
         <v>75</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D54" s="12" t="s">
         <v>360</v>
@@ -6963,10 +6967,10 @@
         <v>183</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -6999,16 +7003,16 @@
         <v>2</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R54" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -7016,19 +7020,19 @@
         <v>76</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>10</v>
@@ -7061,13 +7065,13 @@
         <v>2</v>
       </c>
       <c r="P55" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q55" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R55" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>9</v>
@@ -7084,16 +7088,16 @@
         <v>115</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>388</v>
+        <v>852</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H56" s="3" t="s">
         <v>368</v>
@@ -7119,20 +7123,20 @@
       </c>
       <c r="N56" s="3">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O56" s="3">
         <f t="shared" ref="O56:O99" si="7">SUM(M56:N56)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P56" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R56" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S56" s="12" t="s">
         <v>9</v>
@@ -7152,13 +7156,13 @@
         <v>299</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>56</v>
@@ -7194,10 +7198,10 @@
         <v>93</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R57" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>9</v>
@@ -7223,7 +7227,7 @@
         <v>119</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>56</v>
@@ -7233,7 +7237,7 @@
         <v>208</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="K58" s="3">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7256,13 +7260,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R58" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>9</v>
@@ -7273,7 +7277,7 @@
         <v>82</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>120</v>
@@ -7288,7 +7292,7 @@
         <v>121</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>10</v>
@@ -7321,13 +7325,13 @@
         <v>1</v>
       </c>
       <c r="P59" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R59" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>9</v>
@@ -7341,19 +7345,19 @@
         <v>122</v>
       </c>
       <c r="C60" s="4" t="s">
+        <v>465</v>
+      </c>
+      <c r="D60" s="12" t="s">
         <v>466</v>
       </c>
-      <c r="D60" s="12" t="s">
-        <v>467</v>
-      </c>
       <c r="E60" s="13" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>123</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H60" s="3" t="s">
         <v>368</v>
@@ -7389,13 +7393,13 @@
         <v>93</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R60" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -7409,16 +7413,16 @@
         <v>9</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>837</v>
+        <v>833</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>15</v>
@@ -7451,16 +7455,16 @@
         <v>5</v>
       </c>
       <c r="P61" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R61" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -7468,22 +7472,22 @@
         <v>88</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="E62" s="13" t="s">
         <v>288</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
@@ -7516,13 +7520,13 @@
         <v>4</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R62" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S62" s="12" t="s">
         <v>9</v>
@@ -7536,19 +7540,19 @@
         <v>125</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
@@ -7581,13 +7585,13 @@
         <v>8</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R63" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S63" s="12" t="s">
         <v>9</v>
@@ -7601,19 +7605,19 @@
         <v>126</v>
       </c>
       <c r="C64" s="4" t="s">
+        <v>460</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>461</v>
       </c>
-      <c r="D64" s="12" t="s">
-        <v>462</v>
-      </c>
       <c r="E64" s="13" t="s">
-        <v>838</v>
+        <v>834</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -7649,10 +7653,10 @@
         <v>93</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R64" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S64" s="12" t="s">
         <v>9</v>
@@ -7678,7 +7682,7 @@
         <v>128</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -7711,13 +7715,13 @@
         <v>4</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R65" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>9</v>
@@ -7743,7 +7747,7 @@
         <v>130</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>42</v>
@@ -7776,13 +7780,13 @@
         <v>3</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R66" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>9</v>
@@ -7808,7 +7812,7 @@
         <v>132</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>10</v>
@@ -7841,13 +7845,13 @@
         <v>1</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R67" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S67" s="12" t="s">
         <v>9</v>
@@ -7870,10 +7874,10 @@
         <v>308</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>56</v>
@@ -7906,16 +7910,16 @@
         <v>4</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R68" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -7923,10 +7927,10 @@
         <v>95</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D69" s="13" t="s">
         <v>360</v>
@@ -7935,10 +7939,10 @@
         <v>9</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>21</v>
@@ -7971,16 +7975,16 @@
         <v>1</v>
       </c>
       <c r="P69" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R69" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
@@ -8003,7 +8007,7 @@
         <v>135</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -8036,13 +8040,13 @@
         <v>1</v>
       </c>
       <c r="P70" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R70" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S70" s="12" t="s">
         <v>9</v>
@@ -8053,7 +8057,7 @@
         <v>98</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="C71" s="4" t="s">
         <v>168</v>
@@ -8068,7 +8072,7 @@
         <v>136</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>10</v>
@@ -8101,13 +8105,13 @@
         <v>2</v>
       </c>
       <c r="P71" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R71" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S71" s="12" t="s">
         <v>9</v>
@@ -8118,7 +8122,7 @@
         <v>99</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>9</v>
@@ -8130,10 +8134,10 @@
         <v>508</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>10</v>
@@ -8166,13 +8170,13 @@
         <v>1</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R72" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S72" s="12" t="s">
         <v>9</v>
@@ -8198,7 +8202,7 @@
         <v>138</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>10</v>
@@ -8231,13 +8235,13 @@
         <v>1</v>
       </c>
       <c r="P73" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R73" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S73" s="12" t="s">
         <v>9</v>
@@ -8248,22 +8252,22 @@
         <v>102</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E74" s="13">
         <v>501</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>15</v>
@@ -8296,13 +8300,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R74" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S74" s="12" t="s">
         <v>9</v>
@@ -8313,7 +8317,7 @@
         <v>104</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>9</v>
@@ -8325,10 +8329,10 @@
         <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H75" s="3" t="s">
         <v>368</v>
@@ -8361,13 +8365,13 @@
         <v>2</v>
       </c>
       <c r="P75" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R75" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S75" s="12" t="s">
         <v>9</v>
@@ -8387,13 +8391,13 @@
         <v>374</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>839</v>
+        <v>835</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>142</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8426,13 +8430,13 @@
         <v>7</v>
       </c>
       <c r="P76" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R76" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S76" s="12" t="s">
         <v>9</v>
@@ -8443,13 +8447,13 @@
         <v>108</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E77" s="13" t="s">
         <v>306</v>
@@ -8458,7 +8462,7 @@
         <v>143</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>15</v>
@@ -8491,13 +8495,13 @@
         <v>8</v>
       </c>
       <c r="P77" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R77" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S77" s="12" t="s">
         <v>9</v>
@@ -8508,22 +8512,22 @@
         <v>109</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="D78" s="13" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E78" s="13" t="s">
         <v>310</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8556,16 +8560,16 @@
         <v>7</v>
       </c>
       <c r="P78" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R78" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -8582,13 +8586,13 @@
         <v>9</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H79" s="3" t="s">
         <v>368</v>
@@ -8624,13 +8628,13 @@
         <v>93</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R79" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -8638,22 +8642,22 @@
         <v>113</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H80" s="3" t="s">
         <v>368</v>
@@ -8689,13 +8693,13 @@
         <v>93</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R80" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -8703,22 +8707,22 @@
         <v>114</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>648</v>
+        <v>854</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>46</v>
@@ -8728,7 +8732,7 @@
         <v>207</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K81" s="3">
         <f>VLOOKUP(J81,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8744,20 +8748,20 @@
       </c>
       <c r="N81" s="3">
         <f t="shared" si="9"/>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="O81" s="3">
         <f t="shared" si="7"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="P81" s="12" t="s">
         <v>93</v>
       </c>
       <c r="Q81" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R81" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S81" s="12" t="s">
         <v>9</v>
@@ -8771,7 +8775,7 @@
         <v>146</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>9</v>
@@ -8780,10 +8784,10 @@
         <v>183</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>42</v>
@@ -8816,16 +8820,16 @@
         <v>1</v>
       </c>
       <c r="P82" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R82" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="83" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -8836,10 +8840,10 @@
         <v>147</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="E83" s="13" t="s">
         <v>311</v>
@@ -8848,7 +8852,7 @@
         <v>148</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>30</v>
@@ -8881,13 +8885,13 @@
         <v>5</v>
       </c>
       <c r="P83" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q83" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R83" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S83" s="12" t="s">
         <v>9</v>
@@ -8901,10 +8905,10 @@
         <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="E84" s="13" t="s">
         <v>312</v>
@@ -8913,7 +8917,7 @@
         <v>150</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>30</v>
@@ -8949,10 +8953,10 @@
         <v>93</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R84" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S84" s="12" t="s">
         <v>9</v>
@@ -8978,7 +8982,7 @@
         <v>152</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>21</v>
@@ -9011,13 +9015,13 @@
         <v>1</v>
       </c>
       <c r="P85" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R85" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S85" s="12" t="s">
         <v>9</v>
@@ -9028,10 +9032,10 @@
         <v>120</v>
       </c>
       <c r="B86" t="s">
+        <v>755</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>758</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>761</v>
       </c>
       <c r="D86" s="12" t="s">
         <v>300</v>
@@ -9040,10 +9044,10 @@
         <v>302</v>
       </c>
       <c r="F86" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -9076,16 +9080,16 @@
         <v>3</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q86" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R86" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -9099,16 +9103,16 @@
         <v>176</v>
       </c>
       <c r="D87" s="12" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="E87" s="13" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="F87" s="4" t="s">
         <v>155</v>
       </c>
       <c r="G87" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>15</v>
@@ -9144,10 +9148,10 @@
         <v>93</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R87" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S87" s="12" t="s">
         <v>9</v>
@@ -9161,19 +9165,19 @@
         <v>156</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -9209,13 +9213,13 @@
         <v>93</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R88" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -9223,22 +9227,22 @@
         <v>124</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H89" s="3" t="s">
         <v>368</v>
@@ -9271,16 +9275,16 @@
         <v>9</v>
       </c>
       <c r="P89" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q89" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R89" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9288,10 +9292,10 @@
         <v>126</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="D90" s="12" t="s">
         <v>297</v>
@@ -9300,10 +9304,10 @@
         <v>501</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>46</v>
@@ -9313,7 +9317,7 @@
         <v>207</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K90" s="3">
         <f>VLOOKUP(J90,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9336,13 +9340,13 @@
         <v>2</v>
       </c>
       <c r="P90" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R90" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S90" s="12" t="s">
         <v>9</v>
@@ -9353,22 +9357,22 @@
         <v>127</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="E91" s="13" t="s">
         <v>169</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>46</v>
@@ -9378,7 +9382,7 @@
         <v>207</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9401,16 +9405,16 @@
         <v>4</v>
       </c>
       <c r="P91" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q91" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R91" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9418,10 +9422,10 @@
         <v>128</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D92" s="12" t="s">
         <v>301</v>
@@ -9430,10 +9434,10 @@
         <v>501</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>46</v>
@@ -9443,7 +9447,7 @@
         <v>207</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K92" s="3">
         <f>VLOOKUP(J92,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9466,13 +9470,13 @@
         <v>2</v>
       </c>
       <c r="P92" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R92" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S92" s="12" t="s">
         <v>9</v>
@@ -9483,22 +9487,22 @@
         <v>129</v>
       </c>
       <c r="B93" s="4" t="s">
+        <v>455</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>764</v>
+      </c>
+      <c r="D93" s="12" t="s">
         <v>456</v>
       </c>
-      <c r="C93" s="4" t="s">
-        <v>767</v>
-      </c>
-      <c r="D93" s="12" t="s">
-        <v>457</v>
-      </c>
       <c r="E93" s="13" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>46</v>
@@ -9508,7 +9512,7 @@
         <v>207</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9534,10 +9538,10 @@
         <v>93</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R93" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S93" s="12" t="s">
         <v>9</v>
@@ -9548,10 +9552,10 @@
         <v>130</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
       <c r="D94" s="12" t="s">
         <v>375</v>
@@ -9560,10 +9564,10 @@
         <v>376</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H94" s="3" t="s">
         <v>368</v>
@@ -9596,13 +9600,13 @@
         <v>5</v>
       </c>
       <c r="P94" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q94" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R94" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S94" s="12" t="s">
         <v>9</v>
@@ -9613,22 +9617,22 @@
         <v>133</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>767</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>769</v>
+      </c>
+      <c r="F95" s="4" t="s">
         <v>770</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>771</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>772</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>773</v>
-      </c>
       <c r="G95" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>30</v>
@@ -9664,13 +9668,13 @@
         <v>93</v>
       </c>
       <c r="Q95" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R95" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S95" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9678,7 +9682,7 @@
         <v>134</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>9</v>
@@ -9687,13 +9691,13 @@
         <v>9</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>30</v>
@@ -9729,13 +9733,13 @@
         <v>93</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R96" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S96" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9758,7 +9762,7 @@
         <v>364</v>
       </c>
       <c r="G97" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H97" t="s">
         <v>368</v>
@@ -9791,13 +9795,13 @@
         <v>1</v>
       </c>
       <c r="P97" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q97" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R97" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S97" s="12" t="s">
         <v>9</v>
@@ -9823,7 +9827,7 @@
         <v>365</v>
       </c>
       <c r="G98" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H98" t="s">
         <v>368</v>
@@ -9856,13 +9860,13 @@
         <v>6</v>
       </c>
       <c r="P98" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q98" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R98" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S98" s="12" t="s">
         <v>9</v>
@@ -9873,10 +9877,10 @@
         <v>138</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>9</v>
@@ -9888,7 +9892,7 @@
         <v>363</v>
       </c>
       <c r="G99" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -9921,13 +9925,13 @@
         <v>1</v>
       </c>
       <c r="P99" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q99" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R99" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S99" s="12" t="s">
         <v>9</v>
@@ -9938,7 +9942,7 @@
         <v>139</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>9</v>
@@ -9950,10 +9954,10 @@
         <v>9</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>21</v>
@@ -9986,13 +9990,13 @@
         <v>1</v>
       </c>
       <c r="P100" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R100" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S100" s="12" t="s">
         <v>9</v>
@@ -10003,22 +10007,22 @@
         <v>140</v>
       </c>
       <c r="B101" s="3" t="s">
+        <v>430</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="D101" s="12" t="s">
+        <v>452</v>
+      </c>
+      <c r="E101" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="F101" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="C101" s="4" t="s">
-        <v>791</v>
-      </c>
-      <c r="D101" s="12" t="s">
-        <v>453</v>
-      </c>
-      <c r="E101" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="F101" s="4" t="s">
-        <v>432</v>
-      </c>
       <c r="G101" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>15</v>
@@ -10051,13 +10055,13 @@
         <v>18</v>
       </c>
       <c r="P101" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R101" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S101" s="12">
         <v>2</v>
@@ -10068,22 +10072,22 @@
         <v>141</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>46</v>
@@ -10093,7 +10097,7 @@
         <v>207</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="K102" s="3">
         <f>VLOOKUP(J102,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10116,13 +10120,13 @@
         <v>4</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q102" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R102" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S102" s="12">
         <v>129</v>
@@ -10133,22 +10137,22 @@
         <v>142</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>46</v>
@@ -10158,7 +10162,7 @@
         <v>207</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="K103" s="3">
         <f>VLOOKUP(J103,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10181,13 +10185,13 @@
         <v>3</v>
       </c>
       <c r="P103" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R103" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S103" s="12">
         <v>19</v>
@@ -10198,22 +10202,22 @@
         <v>143</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>9</v>
+        <v>849</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>46</v>
@@ -10223,7 +10227,7 @@
         <v>207</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="K104" s="3">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10231,7 +10235,7 @@
       </c>
       <c r="L104" s="3">
         <f>IF(E104="-",0,1)+IF(D104="-",0,2)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="M104" s="3">
         <f t="shared" si="10"/>
@@ -10239,20 +10243,20 @@
       </c>
       <c r="N104" s="3">
         <f t="shared" si="11"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O104" s="3">
         <f>SUM(M104:N104)</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P104" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R104" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S104" s="12" t="s">
         <v>9</v>
@@ -10263,22 +10267,22 @@
         <v>144</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>15</v>
@@ -10311,16 +10315,16 @@
         <v>1</v>
       </c>
       <c r="P105" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q105" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R105" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S105" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10328,22 +10332,22 @@
         <v>145</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E106" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -10376,16 +10380,16 @@
         <v>1</v>
       </c>
       <c r="P106" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q106" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R106" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10393,22 +10397,22 @@
         <v>146</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D107" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="E107" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="G107" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -10441,16 +10445,16 @@
         <v>6</v>
       </c>
       <c r="P107" s="12" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="Q107" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R107" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="108" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10458,22 +10462,22 @@
         <v>147</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>15</v>
@@ -10506,16 +10510,16 @@
         <v>1</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="Q108" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R108" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
@@ -10523,22 +10527,22 @@
         <v>148</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="D109" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E109" s="13" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>10</v>
@@ -10574,13 +10578,13 @@
         <v>93</v>
       </c>
       <c r="Q109" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R109" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S109" s="12" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="110" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -10588,22 +10592,22 @@
         <v>149</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C110" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>468</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>796</v>
       </c>
-      <c r="D110" s="12" t="s">
-        <v>469</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>799</v>
-      </c>
       <c r="G110" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>21</v>
@@ -10639,13 +10643,13 @@
         <v>93</v>
       </c>
       <c r="Q110" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R110" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -10653,22 +10657,22 @@
         <v>150</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H111" s="3" t="s">
         <v>368</v>
@@ -10704,13 +10708,13 @@
         <v>93</v>
       </c>
       <c r="Q111" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R111" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
@@ -10718,22 +10722,22 @@
         <v>151</v>
       </c>
       <c r="B112" s="3" t="s">
+        <v>479</v>
+      </c>
+      <c r="C112" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D112" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E112" s="13" t="s">
+        <v>477</v>
+      </c>
+      <c r="F112" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="C112" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D112" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E112" s="13" t="s">
-        <v>478</v>
-      </c>
-      <c r="F112" s="4" t="s">
-        <v>481</v>
-      </c>
       <c r="G112" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>15</v>
@@ -10769,10 +10773,10 @@
         <v>93</v>
       </c>
       <c r="Q112" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R112" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S112" s="12" t="s">
         <v>9</v>
@@ -10783,7 +10787,7 @@
         <v>152</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
@@ -10792,13 +10796,13 @@
         <v>9</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H113" s="3" t="s">
         <v>368</v>
@@ -10834,10 +10838,10 @@
         <v>93</v>
       </c>
       <c r="Q113" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R113" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S113" s="12" t="s">
         <v>9</v>
@@ -10848,7 +10852,7 @@
         <v>153</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
@@ -10857,13 +10861,13 @@
         <v>9</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H114" s="3" t="s">
         <v>368</v>
@@ -10899,13 +10903,13 @@
         <v>93</v>
       </c>
       <c r="Q114" s="12" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="R114" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10913,22 +10917,22 @@
         <v>154</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H115" s="3" t="s">
         <v>368</v>
@@ -10964,13 +10968,13 @@
         <v>93</v>
       </c>
       <c r="Q115" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R115" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -10978,22 +10982,22 @@
         <v>155</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="13" t="s">
+        <v>535</v>
+      </c>
+      <c r="F116" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>536</v>
-      </c>
-      <c r="F116" s="4" t="s">
-        <v>535</v>
-      </c>
       <c r="G116" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H116" s="3" t="s">
         <v>368</v>
@@ -11026,16 +11030,16 @@
         <v>2</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q116" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R116" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11043,22 +11047,22 @@
         <v>156</v>
       </c>
       <c r="B117" s="3" t="s">
+        <v>536</v>
+      </c>
+      <c r="C117" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="C117" s="4" t="s">
-        <v>538</v>
-      </c>
       <c r="D117" s="12" t="s">
+        <v>540</v>
+      </c>
+      <c r="E117" s="13" t="s">
         <v>541</v>
       </c>
-      <c r="E117" s="13" t="s">
-        <v>542</v>
-      </c>
       <c r="F117" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="G117" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>30</v>
@@ -11091,13 +11095,13 @@
         <v>2</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q117" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R117" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="S117" s="12" t="s">
         <v>9</v>
@@ -11108,22 +11112,22 @@
         <v>157</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>545</v>
+      </c>
+      <c r="C118" t="s">
         <v>546</v>
       </c>
-      <c r="C118" t="s">
+      <c r="D118" s="12" t="s">
+        <v>558</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>548</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="D118" s="12" t="s">
-        <v>559</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>549</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>548</v>
-      </c>
       <c r="G118" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H118" s="3" t="s">
         <v>368</v>
@@ -11156,16 +11160,16 @@
         <v>5</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q118" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R118" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11173,10 +11177,10 @@
         <v>158</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>9</v>
@@ -11185,10 +11189,10 @@
         <v>505</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>30</v>
@@ -11221,13 +11225,13 @@
         <v>1</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q119" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R119" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S119" s="12" t="s">
         <v>9</v>
@@ -11238,22 +11242,22 @@
         <v>159</v>
       </c>
       <c r="B120" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="C120" t="s">
         <v>661</v>
       </c>
-      <c r="C120" t="s">
-        <v>664</v>
-      </c>
       <c r="D120" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>669</v>
+        <v>666</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -11286,16 +11290,16 @@
         <v>2</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q120" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R120" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>666</v>
+        <v>663</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -11303,22 +11307,22 @@
         <v>160</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="C121" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11351,16 +11355,16 @@
         <v>2</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q121" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R121" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S121" s="12" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
     </row>
     <row r="122" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -11368,22 +11372,22 @@
         <v>161</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>663</v>
+        <v>660</v>
       </c>
       <c r="C122" s="4" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D122" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E122" s="13" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="G122" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>15</v>
@@ -11416,16 +11420,16 @@
         <v>2</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q122" s="12" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="R122" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="S122" s="12" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
     </row>
     <row r="123" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -11433,7 +11437,7 @@
         <v>162</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11442,13 +11446,13 @@
         <v>9</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H123" s="3" t="s">
         <v>368</v>
@@ -11481,16 +11485,16 @@
         <v>1</v>
       </c>
       <c r="P123" s="12" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="Q123" s="12" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="R123" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="S123" s="12" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
   </sheetData>
@@ -11579,8 +11583,8 @@
     <cfRule type="duplicateValues" dxfId="14" priority="12"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J15">
-    <cfRule type="duplicateValues" dxfId="13" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="21"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J32">
     <cfRule type="duplicateValues" dxfId="11" priority="25"/>
@@ -11591,16 +11595,16 @@
     <cfRule type="duplicateValues" dxfId="8" priority="24"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J56">
-    <cfRule type="duplicateValues" dxfId="7" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="19"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J60">
-    <cfRule type="duplicateValues" dxfId="5" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J94">
-    <cfRule type="duplicateValues" dxfId="3" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="8"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -11609,7 +11613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D152"/>
+  <dimension ref="A1:D153"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -11626,7 +11630,7 @@
         <v>279</v>
       </c>
       <c r="C1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D1" s="8" t="s">
         <v>280</v>
@@ -11640,7 +11644,7 @@
         <v>177</v>
       </c>
       <c r="C2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D2" t="s">
         <v>178</v>
@@ -11654,7 +11658,7 @@
         <v>179</v>
       </c>
       <c r="C3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D3" t="s">
         <v>180</v>
@@ -11668,7 +11672,7 @@
         <v>240</v>
       </c>
       <c r="C4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D4" t="s">
         <v>180</v>
@@ -11682,7 +11686,7 @@
         <v>181</v>
       </c>
       <c r="C5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D5" t="s">
         <v>182</v>
@@ -11696,7 +11700,7 @@
         <v>183</v>
       </c>
       <c r="C6" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D6" s="8" t="s">
         <v>184</v>
@@ -11710,7 +11714,7 @@
         <v>185</v>
       </c>
       <c r="C7" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D7" s="8" t="s">
         <v>186</v>
@@ -11724,7 +11728,7 @@
         <v>187</v>
       </c>
       <c r="C8" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D8" s="8" t="s">
         <v>188</v>
@@ -11738,7 +11742,7 @@
         <v>189</v>
       </c>
       <c r="C9" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D9" s="8" t="s">
         <v>190</v>
@@ -11752,7 +11756,7 @@
         <v>191</v>
       </c>
       <c r="C10" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>192</v>
@@ -11766,7 +11770,7 @@
         <v>193</v>
       </c>
       <c r="C11" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>194</v>
@@ -11780,10 +11784,10 @@
         <v>387</v>
       </c>
       <c r="C12" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D12" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11794,7 +11798,7 @@
         <v>195</v>
       </c>
       <c r="C13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D13" s="8" t="s">
         <v>196</v>
@@ -11808,7 +11812,7 @@
         <v>197</v>
       </c>
       <c r="C14" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D14" s="8" t="s">
         <v>198</v>
@@ -11822,7 +11826,7 @@
         <v>199</v>
       </c>
       <c r="C15" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D15" s="8" t="s">
         <v>200</v>
@@ -11836,7 +11840,7 @@
         <v>201</v>
       </c>
       <c r="C16" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D16" s="8" t="s">
         <v>202</v>
@@ -11850,7 +11854,7 @@
         <v>203</v>
       </c>
       <c r="C17" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D17" s="8" t="s">
         <v>204</v>
@@ -11861,13 +11865,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="C18" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D18" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11878,7 +11882,7 @@
         <v>205</v>
       </c>
       <c r="C19" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D19" s="8" t="s">
         <v>206</v>
@@ -11892,7 +11896,7 @@
         <v>207</v>
       </c>
       <c r="C20" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D20" s="8" t="s">
         <v>208</v>
@@ -11906,7 +11910,7 @@
         <v>209</v>
       </c>
       <c r="C21" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D21" s="8" t="s">
         <v>210</v>
@@ -11920,7 +11924,7 @@
         <v>211</v>
       </c>
       <c r="C22" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D22" s="8" t="s">
         <v>212</v>
@@ -11934,7 +11938,7 @@
         <v>213</v>
       </c>
       <c r="C23" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D23" s="8" t="s">
         <v>214</v>
@@ -11948,7 +11952,7 @@
         <v>215</v>
       </c>
       <c r="C24" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D24" s="8" t="s">
         <v>216</v>
@@ -11962,7 +11966,7 @@
         <v>217</v>
       </c>
       <c r="C25" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D25" s="8" t="s">
         <v>218</v>
@@ -11976,7 +11980,7 @@
         <v>219</v>
       </c>
       <c r="C26" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D26" s="8" t="s">
         <v>220</v>
@@ -11990,7 +11994,7 @@
         <v>221</v>
       </c>
       <c r="C27" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D27" s="8" t="s">
         <v>222</v>
@@ -12004,7 +12008,7 @@
         <v>223</v>
       </c>
       <c r="C28" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D28" s="8" t="s">
         <v>224</v>
@@ -12018,7 +12022,7 @@
         <v>225</v>
       </c>
       <c r="C29" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D29" s="8" t="s">
         <v>226</v>
@@ -12032,7 +12036,7 @@
         <v>227</v>
       </c>
       <c r="C30" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D30" s="8" t="s">
         <v>228</v>
@@ -12043,10 +12047,10 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="C31" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D31" s="8" t="s">
         <v>229</v>
@@ -12060,7 +12064,7 @@
         <v>230</v>
       </c>
       <c r="C32" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D32" s="8" t="s">
         <v>231</v>
@@ -12074,24 +12078,24 @@
         <v>232</v>
       </c>
       <c r="C33" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D33" s="8" t="s">
         <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="60" x14ac:dyDescent="0.25">
-      <c r="A34" s="31">
+      <c r="A34" s="10">
         <v>105</v>
       </c>
-      <c r="B34" s="30" t="s">
-        <v>850</v>
-      </c>
-      <c r="C34" s="30" t="s">
-        <v>502</v>
-      </c>
-      <c r="D34" s="32" t="s">
-        <v>851</v>
+      <c r="B34" t="s">
+        <v>846</v>
+      </c>
+      <c r="C34" t="s">
+        <v>501</v>
+      </c>
+      <c r="D34" s="17" t="s">
+        <v>847</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12102,7 +12106,7 @@
         <v>234</v>
       </c>
       <c r="C35" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D35" s="8" t="s">
         <v>235</v>
@@ -12116,7 +12120,7 @@
         <v>236</v>
       </c>
       <c r="C36" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D36" s="8" t="s">
         <v>237</v>
@@ -12130,7 +12134,7 @@
         <v>238</v>
       </c>
       <c r="C37" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D37" s="8" t="s">
         <v>239</v>
@@ -12144,7 +12148,7 @@
         <v>241</v>
       </c>
       <c r="C38" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D38" s="17" t="s">
         <v>242</v>
@@ -12158,7 +12162,7 @@
         <v>243</v>
       </c>
       <c r="C39" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D39" s="8" t="s">
         <v>244</v>
@@ -12172,7 +12176,7 @@
         <v>245</v>
       </c>
       <c r="C40" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D40" s="8" t="s">
         <v>246</v>
@@ -12186,7 +12190,7 @@
         <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D41" s="8" t="s">
         <v>247</v>
@@ -12200,7 +12204,7 @@
         <v>248</v>
       </c>
       <c r="C42" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D42" s="8" t="s">
         <v>249</v>
@@ -12214,7 +12218,7 @@
         <v>250</v>
       </c>
       <c r="C43" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D43" s="8" t="s">
         <v>251</v>
@@ -12225,10 +12229,10 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="C44" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D44" s="8" t="s">
         <v>252</v>
@@ -12239,10 +12243,10 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C45" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D45" s="8" t="s">
         <v>253</v>
@@ -12256,7 +12260,7 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D46" s="8" t="s">
         <v>254</v>
@@ -12270,7 +12274,7 @@
         <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D47" s="8" t="s">
         <v>256</v>
@@ -12284,7 +12288,7 @@
         <v>359</v>
       </c>
       <c r="C48" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D48" t="s">
         <v>386</v>
@@ -12298,7 +12302,7 @@
         <v>157</v>
       </c>
       <c r="C49" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D49" s="8" t="s">
         <v>257</v>
@@ -12312,10 +12316,10 @@
         <v>258</v>
       </c>
       <c r="C50" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12326,7 +12330,7 @@
         <v>158</v>
       </c>
       <c r="C51" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D51" s="8" t="s">
         <v>259</v>
@@ -12340,7 +12344,7 @@
         <v>260</v>
       </c>
       <c r="C52" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D52" s="8" t="s">
         <v>261</v>
@@ -12354,7 +12358,7 @@
         <v>262</v>
       </c>
       <c r="C53" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D53" s="8" t="s">
         <v>263</v>
@@ -12368,7 +12372,7 @@
         <v>264</v>
       </c>
       <c r="C54" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D54" s="8" t="s">
         <v>265</v>
@@ -12382,7 +12386,7 @@
         <v>266</v>
       </c>
       <c r="C55" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D55" s="8" t="s">
         <v>267</v>
@@ -12396,7 +12400,7 @@
         <v>268</v>
       </c>
       <c r="C56" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D56" s="8" t="s">
         <v>269</v>
@@ -12410,7 +12414,7 @@
         <v>270</v>
       </c>
       <c r="C57" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D57" s="8" t="s">
         <v>271</v>
@@ -12424,7 +12428,7 @@
         <v>272</v>
       </c>
       <c r="C58" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D58" s="8" t="s">
         <v>273</v>
@@ -12438,7 +12442,7 @@
         <v>274</v>
       </c>
       <c r="C59" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D59" s="8" t="s">
         <v>275</v>
@@ -12452,7 +12456,7 @@
         <v>276</v>
       </c>
       <c r="C60" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D60" s="8" t="s">
         <v>277</v>
@@ -12466,7 +12470,7 @@
         <v>282</v>
       </c>
       <c r="C61" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D61" s="8" t="s">
         <v>281</v>
@@ -12480,7 +12484,7 @@
         <v>284</v>
       </c>
       <c r="C62" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D62" s="8" t="s">
         <v>283</v>
@@ -12494,7 +12498,7 @@
         <v>161</v>
       </c>
       <c r="C63" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D63" s="8" t="s">
         <v>317</v>
@@ -12508,7 +12512,7 @@
         <v>318</v>
       </c>
       <c r="C64" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D64" s="8" t="s">
         <v>319</v>
@@ -12522,7 +12526,7 @@
         <v>285</v>
       </c>
       <c r="C65" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D65" s="8" t="s">
         <v>320</v>
@@ -12536,10 +12540,10 @@
         <v>50</v>
       </c>
       <c r="C66" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12547,10 +12551,10 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C67" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D67" s="8" t="s">
         <v>286</v>
@@ -12564,7 +12568,7 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D68" s="8" t="s">
         <v>287</v>
@@ -12575,10 +12579,10 @@
         <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="C69" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D69" s="8" t="s">
         <v>321</v>
@@ -12589,13 +12593,13 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="C70" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D70" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
@@ -12606,7 +12610,7 @@
         <v>332</v>
       </c>
       <c r="C71" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D71" s="8" t="s">
         <v>242</v>
@@ -12620,7 +12624,7 @@
         <v>334</v>
       </c>
       <c r="C72" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D72" s="8" t="s">
         <v>242</v>
@@ -12631,10 +12635,10 @@
         <v>335</v>
       </c>
       <c r="B73" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="C73" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D73" s="8" t="s">
         <v>242</v>
@@ -12648,7 +12652,7 @@
         <v>337</v>
       </c>
       <c r="C74" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D74" s="8" t="s">
         <v>242</v>
@@ -12662,7 +12666,7 @@
         <v>140</v>
       </c>
       <c r="C75" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D75" s="8" t="s">
         <v>242</v>
@@ -12676,7 +12680,7 @@
         <v>340</v>
       </c>
       <c r="C76" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D76" s="8" t="s">
         <v>242</v>
@@ -12690,7 +12694,7 @@
         <v>342</v>
       </c>
       <c r="C77" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D77" s="8" t="s">
         <v>242</v>
@@ -12704,7 +12708,7 @@
         <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D78" s="8" t="s">
         <v>242</v>
@@ -12715,10 +12719,10 @@
         <v>344</v>
       </c>
       <c r="B79" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C79" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D79" s="8" t="s">
         <v>242</v>
@@ -12729,10 +12733,10 @@
         <v>345</v>
       </c>
       <c r="B80" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C80" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D80" s="8" t="s">
         <v>242</v>
@@ -12743,10 +12747,10 @@
         <v>314</v>
       </c>
       <c r="B81" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C81" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D81" s="8" t="s">
         <v>242</v>
@@ -12757,10 +12761,10 @@
         <v>346</v>
       </c>
       <c r="B82" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C82" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D82" s="8" t="s">
         <v>242</v>
@@ -12774,7 +12778,7 @@
         <v>348</v>
       </c>
       <c r="C83" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D83" s="8" t="s">
         <v>242</v>
@@ -12788,7 +12792,7 @@
         <v>350</v>
       </c>
       <c r="C84" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D84" s="8" t="s">
         <v>242</v>
@@ -12802,7 +12806,7 @@
         <v>158</v>
       </c>
       <c r="C85" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D85" s="8" t="s">
         <v>242</v>
@@ -12816,7 +12820,7 @@
         <v>353</v>
       </c>
       <c r="C86" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D86" s="8" t="s">
         <v>242</v>
@@ -12830,7 +12834,7 @@
         <v>355</v>
       </c>
       <c r="C87" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D87" s="8" t="s">
         <v>242</v>
@@ -12844,7 +12848,7 @@
         <v>357</v>
       </c>
       <c r="C88" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D88" s="8" t="s">
         <v>242</v>
@@ -12858,7 +12862,7 @@
         <v>359</v>
       </c>
       <c r="C89" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D89" s="8" t="s">
         <v>242</v>
@@ -12872,7 +12876,7 @@
         <v>357</v>
       </c>
       <c r="C90" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D90" s="8" t="s">
         <v>244</v>
@@ -12886,7 +12890,7 @@
         <v>240</v>
       </c>
       <c r="C91" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D91" s="8" t="s">
         <v>244</v>
@@ -12897,10 +12901,10 @@
         <v>360</v>
       </c>
       <c r="B92" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C92" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D92" s="8" t="s">
         <v>251</v>
@@ -12914,7 +12918,7 @@
         <v>101</v>
       </c>
       <c r="C93" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D93" s="8" t="s">
         <v>256</v>
@@ -12928,7 +12932,7 @@
         <v>240</v>
       </c>
       <c r="C94" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D94" s="8" t="s">
         <v>196</v>
@@ -12942,7 +12946,7 @@
         <v>158</v>
       </c>
       <c r="C95" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D95" s="8" t="s">
         <v>259</v>
@@ -12956,7 +12960,7 @@
         <v>240</v>
       </c>
       <c r="C96" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D96" s="8" t="s">
         <v>202</v>
@@ -12970,7 +12974,7 @@
         <v>323</v>
       </c>
       <c r="C97" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D97" s="8" t="s">
         <v>281</v>
@@ -12984,7 +12988,7 @@
         <v>58</v>
       </c>
       <c r="C98" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D98" s="8" t="s">
         <v>281</v>
@@ -12998,7 +13002,7 @@
         <v>62</v>
       </c>
       <c r="C99" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D99" s="8" t="s">
         <v>281</v>
@@ -13012,7 +13016,7 @@
         <v>325</v>
       </c>
       <c r="C100" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D100" s="8" t="s">
         <v>281</v>
@@ -13026,7 +13030,7 @@
         <v>327</v>
       </c>
       <c r="C101" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D101" s="8" t="s">
         <v>281</v>
@@ -13040,7 +13044,7 @@
         <v>329</v>
       </c>
       <c r="C102" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D102" s="8" t="s">
         <v>281</v>
@@ -13054,7 +13058,7 @@
         <v>19</v>
       </c>
       <c r="C103" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D103" s="8" t="s">
         <v>281</v>
@@ -13068,7 +13072,7 @@
         <v>140</v>
       </c>
       <c r="C104" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D104" s="8" t="s">
         <v>281</v>
@@ -13082,7 +13086,7 @@
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D105" s="8" t="s">
         <v>281</v>
@@ -13093,10 +13097,10 @@
         <v>330</v>
       </c>
       <c r="B106" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="C106" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D106" s="8" t="s">
         <v>281</v>
@@ -13110,7 +13114,7 @@
         <v>157</v>
       </c>
       <c r="C107" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D107" s="8" t="s">
         <v>281</v>
@@ -13121,10 +13125,10 @@
         <v>299</v>
       </c>
       <c r="B108" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C108" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D108" s="8" t="s">
         <v>281</v>
@@ -13135,10 +13139,10 @@
         <v>300</v>
       </c>
       <c r="B109" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C109" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D109" s="8" t="s">
         <v>281</v>
@@ -13152,7 +13156,7 @@
         <v>158</v>
       </c>
       <c r="C110" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D110" s="8" t="s">
         <v>281</v>
@@ -13166,7 +13170,7 @@
         <v>33</v>
       </c>
       <c r="C111" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D111" s="8" t="s">
         <v>281</v>
@@ -13180,7 +13184,7 @@
         <v>240</v>
       </c>
       <c r="C112" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D112" s="8" t="s">
         <v>178</v>
@@ -13194,7 +13198,7 @@
         <v>240</v>
       </c>
       <c r="C113" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D113" s="8" t="s">
         <v>180</v>
@@ -13202,391 +13206,391 @@
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
+        <v>400</v>
+      </c>
+      <c r="B114" t="s">
         <v>401</v>
       </c>
-      <c r="B114" t="s">
-        <v>402</v>
-      </c>
       <c r="C114" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D114" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="B115" t="s">
         <v>359</v>
       </c>
       <c r="C115" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D115" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B116" t="s">
         <v>240</v>
       </c>
       <c r="C116" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D116" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B117" t="s">
         <v>332</v>
       </c>
       <c r="C117" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D117" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B118" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="C118" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D118" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B119" t="s">
         <v>140</v>
       </c>
       <c r="C119" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D119" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="B120" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="C120" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D120" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B121" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="C121" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D121" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B122" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="C122" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D122" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B123" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C123" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D123" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B124" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C124" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D124" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B125" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="C125" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D125" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B126" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="C126" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D126" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B127" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="C127" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D127" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B128" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="C128" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D128" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B129" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="C129" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D129" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B130" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C130" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D130" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
+        <v>450</v>
+      </c>
+      <c r="B131" t="s">
         <v>451</v>
       </c>
-      <c r="B131" t="s">
-        <v>452</v>
-      </c>
       <c r="C131" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D131" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B132" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C132" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D132" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B133" t="s">
         <v>255</v>
       </c>
       <c r="C133" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D133" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
+        <v>482</v>
+      </c>
+      <c r="B134" t="s">
+        <v>484</v>
+      </c>
+      <c r="C134" t="s">
+        <v>501</v>
+      </c>
+      <c r="D134" t="s">
         <v>483</v>
-      </c>
-      <c r="B134" t="s">
-        <v>485</v>
-      </c>
-      <c r="C134" t="s">
-        <v>502</v>
-      </c>
-      <c r="D134" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
+        <v>523</v>
+      </c>
+      <c r="B135" t="s">
         <v>524</v>
       </c>
-      <c r="B135" t="s">
+      <c r="C135" t="s">
+        <v>501</v>
+      </c>
+      <c r="D135" t="s">
         <v>525</v>
-      </c>
-      <c r="C135" t="s">
-        <v>502</v>
-      </c>
-      <c r="D135" t="s">
-        <v>526</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B136" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C136" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D136" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B137" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="C137" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D137" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
+        <v>548</v>
+      </c>
+      <c r="B138" t="s">
+        <v>550</v>
+      </c>
+      <c r="C138" t="s">
+        <v>501</v>
+      </c>
+      <c r="D138" t="s">
         <v>549</v>
-      </c>
-      <c r="B138" t="s">
-        <v>551</v>
-      </c>
-      <c r="C138" t="s">
-        <v>502</v>
-      </c>
-      <c r="D138" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
+        <v>551</v>
+      </c>
+      <c r="B139" t="s">
+        <v>490</v>
+      </c>
+      <c r="C139" t="s">
+        <v>492</v>
+      </c>
+      <c r="D139" t="s">
         <v>552</v>
-      </c>
-      <c r="B139" t="s">
-        <v>491</v>
-      </c>
-      <c r="C139" t="s">
-        <v>493</v>
-      </c>
-      <c r="D139" t="s">
-        <v>553</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B140" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C140" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D140" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B141" t="s">
         <v>240</v>
       </c>
       <c r="C141" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D141" t="s">
         <v>239</v>
@@ -13594,156 +13598,170 @@
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B142" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="C142" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D142" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
+        <v>565</v>
+      </c>
+      <c r="B143" t="s">
+        <v>580</v>
+      </c>
+      <c r="C143" t="s">
+        <v>492</v>
+      </c>
+      <c r="D143" t="s">
         <v>566</v>
-      </c>
-      <c r="B143" t="s">
-        <v>582</v>
-      </c>
-      <c r="C143" t="s">
-        <v>493</v>
-      </c>
-      <c r="D143" t="s">
-        <v>567</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
+        <v>568</v>
+      </c>
+      <c r="B144" t="s">
         <v>569</v>
       </c>
-      <c r="B144" t="s">
+      <c r="C144" t="s">
+        <v>501</v>
+      </c>
+      <c r="D144" t="s">
         <v>570</v>
-      </c>
-      <c r="C144" t="s">
-        <v>502</v>
-      </c>
-      <c r="D144" t="s">
-        <v>571</v>
       </c>
     </row>
     <row r="145" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="B145" t="s">
         <v>157</v>
       </c>
       <c r="C145" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D145" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
     </row>
     <row r="146" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B146" t="s">
         <v>140</v>
       </c>
       <c r="C146" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="147" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
+        <v>638</v>
+      </c>
+      <c r="B147" t="s">
+        <v>639</v>
+      </c>
+      <c r="C147" t="s">
+        <v>501</v>
+      </c>
+      <c r="D147" t="s">
         <v>640</v>
-      </c>
-      <c r="B147" t="s">
-        <v>641</v>
-      </c>
-      <c r="C147" t="s">
-        <v>502</v>
-      </c>
-      <c r="D147" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="148" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="B148" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C148" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D148" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
     </row>
     <row r="149" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A149" s="10" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="B149" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C149" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D149" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
     </row>
     <row r="150" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="B150" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="C150" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D150" t="s">
-        <v>681</v>
+        <v>678</v>
       </c>
     </row>
     <row r="151" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A151" s="10" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="B151" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="C151" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D151" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
     </row>
     <row r="152" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="B152" t="s">
-        <v>840</v>
+        <v>836</v>
       </c>
       <c r="C152" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D152" t="s">
-        <v>833</v>
+        <v>830</v>
+      </c>
+    </row>
+    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A153" s="10" t="s">
+        <v>849</v>
+      </c>
+      <c r="B153" t="s">
+        <v>850</v>
+      </c>
+      <c r="C153" t="s">
+        <v>501</v>
+      </c>
+      <c r="D153" t="s">
+        <v>848</v>
       </c>
     </row>
   </sheetData>
@@ -13941,7 +13959,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="B11">
         <v>311</v>
@@ -13949,7 +13967,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="B12">
         <v>312</v>
@@ -13981,7 +13999,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="B16">
         <v>317</v>
@@ -14109,7 +14127,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -14135,50 +14153,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>492</v>
+      </c>
+      <c r="B2" s="10" t="s">
         <v>493</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>494</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
+        <v>496</v>
+      </c>
+      <c r="B4" s="10" t="s">
         <v>497</v>
-      </c>
-      <c r="B4" s="10" t="s">
-        <v>498</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
+        <v>499</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>500</v>
-      </c>
-      <c r="B5" s="10" t="s">
-        <v>501</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
+        <v>501</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>502</v>
-      </c>
-      <c r="B6" s="10" t="s">
-        <v>503</v>
       </c>
     </row>
   </sheetData>

--- a/dataset/DevEx_Metrics.xlsx
+++ b/dataset/DevEx_Metrics.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DATA\DEV\UZH\DX-Metrics-Compass\dataset\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE71621-B85A-4D55-81B5-B84F70F7D653}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6681309D-EE8E-4A8E-B74D-2EC921A8556F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28695" yWindow="0" windowWidth="29010" windowHeight="23385" tabRatio="506" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2048" uniqueCount="855">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2078" uniqueCount="872">
   <si>
     <t>id</t>
   </si>
@@ -491,9 +491,6 @@
     <t>Technical Debt Ratio</t>
   </si>
   <si>
-    <t>Is an estimate of maintenance burden in codebase. It essentially compares the cost of fixing existing technical debt to the total cost of developing the software.</t>
-  </si>
-  <si>
     <t>Maintenance Burden</t>
   </si>
   <si>
@@ -978,9 +975,6 @@
   </si>
   <si>
     <t>508; 501; 131</t>
-  </si>
-  <si>
-    <t>70; 131</t>
   </si>
   <si>
     <t>105; 234; 235; 131</t>
@@ -2301,9 +2295,6 @@
     <t>17; 121</t>
   </si>
   <si>
-    <t>Technical Debt; Time Spent Remediating Tech Debt</t>
-  </si>
-  <si>
     <t>202a; 511i; 511l; 183a; 501h</t>
   </si>
   <si>
@@ -2611,6 +2602,66 @@
   </si>
   <si>
     <t>506; 9; 13; 15; 45; 87; 233; 235; 236; 237; 238; 513; 523</t>
+  </si>
+  <si>
+    <t>Is an estimate of maintenance burden in codebase. It expresses the cost of fixing existing technical debt as a proportion of the total cost of developing the software (i.e. remediation cost ÷ development cost).</t>
+  </si>
+  <si>
+    <t>Technical Debt; Time Spent Remediating Techical Debt; Tech Debt</t>
+  </si>
+  <si>
+    <t>163</t>
+  </si>
+  <si>
+    <t>Cognitive Debt Ratio</t>
+  </si>
+  <si>
+    <t>524a</t>
+  </si>
+  <si>
+    <t>524b</t>
+  </si>
+  <si>
+    <t>https://www.sonarsource.com/resources/library/measuring-and-identifying-code-level-technical-debt-a-practical-guide/</t>
+  </si>
+  <si>
+    <t>https://getdx.com/blog/technical-debt-ratio/</t>
+  </si>
+  <si>
+    <t>Reference-for-Implementation</t>
+  </si>
+  <si>
+    <t>70; 131; 524a; 524b</t>
+  </si>
+  <si>
+    <t>https://arxiv.org/abs/2603.22106</t>
+  </si>
+  <si>
+    <t>Storey (2026)</t>
+  </si>
+  <si>
+    <t>525a; 525b</t>
+  </si>
+  <si>
+    <t>https://dl.acm.org/doi/10.1145/3794763.3794804</t>
+  </si>
+  <si>
+    <t>525b</t>
+  </si>
+  <si>
+    <t>525a</t>
+  </si>
+  <si>
+    <t>Alakmeh (2026)</t>
+  </si>
+  <si>
+    <t>Comprehension Debt; Shared Understanding Erosion</t>
+  </si>
+  <si>
+    <t>116; 20</t>
+  </si>
+  <si>
+    <t>A construct (not yet a validated metric) describing the team- and project-level erosion of shared understanding of a software system over time, as the mental models developers rely on to reason about and safely change the system become inadequate. No agreed measurement exists yet. Candidate signals proposed in research include low bus factor / knowledge concentration, slow onboarding, resistance to change, and the gap between code developers can produce with AI and what they genuinely understand ("comprehension debt").</t>
   </si>
 </sst>
 </file>
@@ -2708,7 +2759,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
@@ -2788,6 +2839,10 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3491,7 +3546,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S123"/>
+  <dimension ref="A1:S137"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="3"/>
@@ -3522,16 +3577,16 @@
         <v>2</v>
       </c>
       <c r="D1" s="11" t="s">
+        <v>158</v>
+      </c>
+      <c r="E1" s="11" t="s">
         <v>159</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>160</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>4</v>
@@ -3549,25 +3604,25 @@
         <v>8</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="N1" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>367</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>369</v>
-      </c>
       <c r="P1" s="15" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="Q1" s="15" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="S1" s="15" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
     </row>
     <row r="2" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -3581,16 +3636,16 @@
         <v>13</v>
       </c>
       <c r="D2" s="12" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="E2" s="13" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>15</v>
@@ -3623,16 +3678,16 @@
         <v>23</v>
       </c>
       <c r="P2" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q2" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S2" s="12" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
     </row>
     <row r="3" spans="1:19" x14ac:dyDescent="0.25">
@@ -3655,7 +3710,7 @@
         <v>20</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>21</v>
@@ -3688,13 +3743,13 @@
         <v>1</v>
       </c>
       <c r="P3" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q3" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R3" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S3" s="12" t="s">
         <v>9</v>
@@ -3705,22 +3760,22 @@
         <v>9</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D4" s="12" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E4" s="13" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>15</v>
@@ -3753,16 +3808,16 @@
         <v>4</v>
       </c>
       <c r="P4" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q4" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R4" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S4" s="12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="5" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -3770,25 +3825,25 @@
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D5" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E5" s="13" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I5" s="3">
         <f>VLOOKUP(H5,cardsort_group_IDs!A:B,2,0)</f>
@@ -3818,13 +3873,13 @@
         <v>5</v>
       </c>
       <c r="P5" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q5" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R5" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S5" s="12" t="s">
         <v>9</v>
@@ -3850,7 +3905,7 @@
         <v>28</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>10</v>
@@ -3883,13 +3938,13 @@
         <v>1</v>
       </c>
       <c r="P6" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q6" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R6" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S6" s="12" t="s">
         <v>9</v>
@@ -3903,19 +3958,19 @@
         <v>29</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>30</v>
@@ -3951,13 +4006,13 @@
         <v>93</v>
       </c>
       <c r="Q7" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R7" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S7" s="12" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -3971,16 +4026,16 @@
         <v>9</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="F8" s="4" t="s">
         <v>34</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>30</v>
@@ -4013,13 +4068,13 @@
         <v>2</v>
       </c>
       <c r="P8" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q8" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R8" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S8" s="12" t="s">
         <v>9</v>
@@ -4036,16 +4091,16 @@
         <v>9</v>
       </c>
       <c r="D9" s="12" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="E9" s="13" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="F9" s="4" t="s">
         <v>37</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>30</v>
@@ -4078,13 +4133,13 @@
         <v>4</v>
       </c>
       <c r="P9" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q9" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R9" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S9" s="12" t="s">
         <v>9</v>
@@ -4095,22 +4150,22 @@
         <v>15</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>606</v>
+      </c>
+      <c r="D10" s="12" t="s">
+        <v>605</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>682</v>
+      </c>
+      <c r="F10" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="D10" s="12" t="s">
-        <v>607</v>
-      </c>
-      <c r="E10" s="13" t="s">
-        <v>684</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>610</v>
-      </c>
       <c r="G10" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>15</v>
@@ -4143,13 +4198,13 @@
         <v>5</v>
       </c>
       <c r="P10" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q10" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R10" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S10" s="12" t="s">
         <v>9</v>
@@ -4166,16 +4221,16 @@
         <v>9</v>
       </c>
       <c r="D11" s="12" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>39</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>30</v>
@@ -4208,13 +4263,13 @@
         <v>5</v>
       </c>
       <c r="P11" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q11" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R11" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S11" s="12" t="s">
         <v>9</v>
@@ -4225,22 +4280,22 @@
         <v>17</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="E12" s="13" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F12" s="4" t="s">
         <v>41</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>42</v>
@@ -4250,7 +4305,7 @@
         <v>206</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="K12" s="3">
         <f>VLOOKUP(J12,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4273,13 +4328,13 @@
         <v>11</v>
       </c>
       <c r="P12" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q12" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R12" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S12" s="12" t="s">
         <v>9</v>
@@ -4293,19 +4348,19 @@
         <v>43</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="D13" s="12" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>44</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>30</v>
@@ -4341,10 +4396,10 @@
         <v>93</v>
       </c>
       <c r="Q13" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R13" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S13" s="12" t="s">
         <v>9</v>
@@ -4358,19 +4413,19 @@
         <v>45</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="D14" s="12" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="E14" s="13" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>46</v>
@@ -4380,7 +4435,7 @@
         <v>207</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="K14" s="3">
         <f>VLOOKUP(J14,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4403,13 +4458,13 @@
         <v>25</v>
       </c>
       <c r="P14" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q14" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R14" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S14" s="12" t="s">
         <v>9</v>
@@ -4420,25 +4475,25 @@
         <v>20</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D15" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="13" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H15" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I15" s="3">
         <f>VLOOKUP(H15,cardsort_group_IDs!A:B,2,0)</f>
@@ -4471,10 +4526,10 @@
         <v>93</v>
       </c>
       <c r="Q15" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R15" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S15" s="12" t="s">
         <v>9</v>
@@ -4485,22 +4540,22 @@
         <v>22</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="C16" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D16" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E16" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F16" s="4" t="s">
         <v>49</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>15</v>
@@ -4533,13 +4588,13 @@
         <v>3</v>
       </c>
       <c r="P16" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q16" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R16" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S16" s="12" t="s">
         <v>9</v>
@@ -4550,22 +4605,22 @@
         <v>23</v>
       </c>
       <c r="B17" s="24" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D17" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E17" s="13" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="F17" s="5" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>42</v>
@@ -4598,16 +4653,16 @@
         <v>2</v>
       </c>
       <c r="P17" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q17" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R17" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S17" s="12" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="18" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -4630,7 +4685,7 @@
         <v>54</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>10</v>
@@ -4663,13 +4718,13 @@
         <v>1</v>
       </c>
       <c r="P18" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q18" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R18" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S18" s="12" t="s">
         <v>9</v>
@@ -4680,22 +4735,22 @@
         <v>25</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D19" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E19" s="13" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="F19" s="4" t="s">
         <v>55</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>56</v>
@@ -4705,7 +4760,7 @@
         <v>208</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="K19" s="3">
         <f>VLOOKUP(J19,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4728,13 +4783,13 @@
         <v>3</v>
       </c>
       <c r="P19" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q19" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R19" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S19" s="12" t="s">
         <v>9</v>
@@ -4745,22 +4800,22 @@
         <v>26</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="C20" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D20" s="12" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E20" s="13">
         <v>131</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>56</v>
@@ -4770,7 +4825,7 @@
         <v>208</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="K20" s="3">
         <f>VLOOKUP(J20,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -4793,16 +4848,16 @@
         <v>3</v>
       </c>
       <c r="P20" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q20" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R20" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S20" s="12" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
     </row>
     <row r="21" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -4813,19 +4868,19 @@
         <v>24</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="D21" s="13" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="F21" s="4" t="s">
         <v>57</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>15</v>
@@ -4861,10 +4916,10 @@
         <v>93</v>
       </c>
       <c r="Q21" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R21" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S21" s="12" t="s">
         <v>9</v>
@@ -4875,22 +4930,22 @@
         <v>29</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="D22" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>30</v>
@@ -4923,13 +4978,13 @@
         <v>3</v>
       </c>
       <c r="P22" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q22" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R22" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S22" s="12" t="s">
         <v>9</v>
@@ -4946,16 +5001,16 @@
         <v>9</v>
       </c>
       <c r="D23" s="13" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E23" s="13" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H23" s="3" t="s">
         <v>56</v>
@@ -4991,13 +5046,13 @@
         <v>93</v>
       </c>
       <c r="Q23" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R23" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S23" s="12" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.25">
@@ -5008,19 +5063,19 @@
         <v>60</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="D24" s="12">
         <v>170</v>
       </c>
       <c r="E24" s="13" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F24" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>30</v>
@@ -5053,16 +5108,16 @@
         <v>5</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q24" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R24" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S24" s="12" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="25" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -5070,13 +5125,13 @@
         <v>32</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C25" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D25" s="12" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E25" s="13">
         <v>501</v>
@@ -5085,7 +5140,7 @@
         <v>63</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>56</v>
@@ -5118,13 +5173,13 @@
         <v>2</v>
       </c>
       <c r="P25" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q25" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R25" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S25" s="12" t="s">
         <v>9</v>
@@ -5141,16 +5196,16 @@
         <v>9</v>
       </c>
       <c r="D26" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E26" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F26" s="4" t="s">
         <v>65</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>15</v>
@@ -5183,13 +5238,13 @@
         <v>3</v>
       </c>
       <c r="P26" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q26" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R26" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S26" s="12" t="s">
         <v>9</v>
@@ -5203,19 +5258,19 @@
         <v>67</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="D27" s="13" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>21</v>
@@ -5248,13 +5303,13 @@
         <v>6</v>
       </c>
       <c r="P27" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q27" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R27" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S27" s="12" t="s">
         <v>9</v>
@@ -5268,22 +5323,22 @@
         <v>69</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="D28" s="13" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="E28" s="13" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="F28" s="4" t="s">
         <v>70</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I28" s="3">
         <f>VLOOKUP(H28,cardsort_group_IDs!A:B,2,0)</f>
@@ -5316,13 +5371,13 @@
         <v>93</v>
       </c>
       <c r="Q28" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R28" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S28" s="12" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="29" spans="1:19" ht="165" x14ac:dyDescent="0.25">
@@ -5330,7 +5385,7 @@
         <v>37</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="C29" s="4" t="s">
         <v>9</v>
@@ -5345,7 +5400,7 @@
         <v>72</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>10</v>
@@ -5378,13 +5433,13 @@
         <v>1</v>
       </c>
       <c r="P29" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q29" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R29" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S29" s="12" t="s">
         <v>9</v>
@@ -5398,19 +5453,19 @@
         <v>73</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="D30" s="12" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E30" s="13" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F30" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="G30" s="3" t="s">
         <v>517</v>
-      </c>
-      <c r="G30" s="3" t="s">
-        <v>519</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>15</v>
@@ -5446,10 +5501,10 @@
         <v>93</v>
       </c>
       <c r="Q30" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R30" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S30" s="12" t="s">
         <v>9</v>
@@ -5466,16 +5521,16 @@
         <v>9</v>
       </c>
       <c r="D31" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F31" s="4" t="s">
         <v>75</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>15</v>
@@ -5508,13 +5563,13 @@
         <v>3</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q31" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R31" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S31" s="12" t="s">
         <v>9</v>
@@ -5531,19 +5586,19 @@
         <v>76</v>
       </c>
       <c r="D32" s="13" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="E32" s="13" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="F32" s="4" t="s">
         <v>77</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I32" s="3">
         <f>VLOOKUP(H32,cardsort_group_IDs!A:B,2,0)</f>
@@ -5576,10 +5631,10 @@
         <v>93</v>
       </c>
       <c r="Q32" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R32" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S32" s="12" t="s">
         <v>9</v>
@@ -5593,22 +5648,22 @@
         <v>78</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D33" s="12" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="E33" s="13" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>79</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I33" s="3">
         <f>VLOOKUP(H33,cardsort_group_IDs!A:B,2,0)</f>
@@ -5638,13 +5693,13 @@
         <v>6</v>
       </c>
       <c r="P33" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q33" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R33" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S33" s="12" t="s">
         <v>9</v>
@@ -5658,19 +5713,19 @@
         <v>80</v>
       </c>
       <c r="C34" s="4" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E34" s="13" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="F34" s="4" t="s">
         <v>81</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H34" s="3" t="s">
         <v>30</v>
@@ -5703,16 +5758,16 @@
         <v>3</v>
       </c>
       <c r="P34" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q34" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R34" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S34" s="12" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
     </row>
     <row r="35" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -5726,19 +5781,19 @@
         <v>9</v>
       </c>
       <c r="D35" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E35" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>83</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I35" s="3">
         <f>VLOOKUP(H35,cardsort_group_IDs!A:B,2,0)</f>
@@ -5768,13 +5823,13 @@
         <v>3</v>
       </c>
       <c r="P35" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q35" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R35" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S35" s="12" t="s">
         <v>9</v>
@@ -5788,19 +5843,19 @@
         <v>85</v>
       </c>
       <c r="C36" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="D36" s="13" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E36" s="13" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="F36" s="4" t="s">
         <v>87</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>21</v>
@@ -5836,10 +5891,10 @@
         <v>93</v>
       </c>
       <c r="Q36" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R36" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S36" s="12" t="s">
         <v>9</v>
@@ -5859,13 +5914,13 @@
         <v>9</v>
       </c>
       <c r="E37" s="13" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F37" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>21</v>
@@ -5898,13 +5953,13 @@
         <v>2</v>
       </c>
       <c r="P37" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q37" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R37" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S37" s="12" t="s">
         <v>9</v>
@@ -5915,22 +5970,22 @@
         <v>46</v>
       </c>
       <c r="B38" s="3" t="s">
+        <v>706</v>
+      </c>
+      <c r="C38" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>710</v>
-      </c>
       <c r="D38" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E38" s="13" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>42</v>
@@ -5966,10 +6021,10 @@
         <v>93</v>
       </c>
       <c r="Q38" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R38" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S38" s="12" t="s">
         <v>9</v>
@@ -5980,25 +6035,25 @@
         <v>50</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="D39" s="12" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E39" s="13" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H39" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I39" s="3">
         <f>VLOOKUP(H39,cardsort_group_IDs!A:B,2,0)</f>
@@ -6028,16 +6083,16 @@
         <v>13</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q39" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R39" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S39" s="12" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="40" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -6048,22 +6103,22 @@
         <v>93</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D40" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E40" s="13" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F40" s="4" t="s">
         <v>94</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I40" s="3">
         <f>VLOOKUP(H40,cardsort_group_IDs!A:B,2,0)</f>
@@ -6093,13 +6148,13 @@
         <v>4</v>
       </c>
       <c r="P40" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q40" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R40" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S40" s="12" t="s">
         <v>9</v>
@@ -6125,7 +6180,7 @@
         <v>96</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>10</v>
@@ -6158,13 +6213,13 @@
         <v>1</v>
       </c>
       <c r="P41" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q41" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R41" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S41" s="12" t="s">
         <v>9</v>
@@ -6178,22 +6233,22 @@
         <v>97</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D42" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E42" s="13" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="G42" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I42" s="3">
         <f>VLOOKUP(H42,cardsort_group_IDs!A:B,2,0)</f>
@@ -6226,13 +6281,13 @@
         <v>93</v>
       </c>
       <c r="Q42" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R42" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S42" s="12" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.25">
@@ -6240,25 +6295,25 @@
         <v>59</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="13" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F43" s="4" t="s">
         <v>98</v>
       </c>
       <c r="G43" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H43" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I43" s="3">
         <f>VLOOKUP(H43,cardsort_group_IDs!A:B,2,0)</f>
@@ -6291,13 +6346,13 @@
         <v>93</v>
       </c>
       <c r="Q43" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R43" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S43" s="12" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
     </row>
     <row r="44" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -6305,22 +6360,22 @@
         <v>62</v>
       </c>
       <c r="B44" s="24" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="C44" s="5" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="D44" s="13" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="E44" s="13" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="G44" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H44" s="3" t="s">
         <v>15</v>
@@ -6353,13 +6408,13 @@
         <v>14</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q44" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R44" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S44" s="12" t="s">
         <v>9</v>
@@ -6373,19 +6428,19 @@
         <v>100</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="E45" s="13" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F45" s="4" t="s">
         <v>102</v>
       </c>
       <c r="G45" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>30</v>
@@ -6421,10 +6476,10 @@
         <v>93</v>
       </c>
       <c r="Q45" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R45" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S45" s="12" t="s">
         <v>9</v>
@@ -6447,10 +6502,10 @@
         <v>9</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="G46" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H46" s="3" t="s">
         <v>21</v>
@@ -6483,13 +6538,13 @@
         <v>1</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q46" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R46" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S46" s="12" t="s">
         <v>9</v>
@@ -6503,19 +6558,19 @@
         <v>104</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="D47" s="13" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="E47" s="13" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F47" s="4" t="s">
         <v>105</v>
       </c>
       <c r="G47" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H47" s="3" t="s">
         <v>21</v>
@@ -6548,13 +6603,13 @@
         <v>16</v>
       </c>
       <c r="P47" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q47" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R47" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S47" s="12" t="s">
         <v>9</v>
@@ -6565,22 +6620,22 @@
         <v>67</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="C48" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D48" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E48" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F48" s="4" t="s">
         <v>106</v>
       </c>
       <c r="G48" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H48" s="3" t="s">
         <v>42</v>
@@ -6613,13 +6668,13 @@
         <v>3</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q48" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R48" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S48" s="12" t="s">
         <v>9</v>
@@ -6633,19 +6688,19 @@
         <v>107</v>
       </c>
       <c r="C49" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E49" s="13" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F49" s="4" t="s">
         <v>108</v>
       </c>
       <c r="G49" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H49" s="3" t="s">
         <v>56</v>
@@ -6678,13 +6733,13 @@
         <v>3</v>
       </c>
       <c r="P49" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q49" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R49" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S49" s="12" t="s">
         <v>9</v>
@@ -6698,19 +6753,19 @@
         <v>109</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E50" s="13" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="G50" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H50" s="3" t="s">
         <v>30</v>
@@ -6743,16 +6798,16 @@
         <v>5</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q50" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R50" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S50" s="12" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="51" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -6760,22 +6815,22 @@
         <v>71</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C51" s="4" t="s">
         <v>92</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E51" s="13" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="G51" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H51" s="3" t="s">
         <v>15</v>
@@ -6808,13 +6863,13 @@
         <v>4</v>
       </c>
       <c r="P51" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q51" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R51" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S51" s="12" t="s">
         <v>9</v>
@@ -6825,22 +6880,22 @@
         <v>72</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="C52" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D52" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E52" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="G52" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H52" s="3" t="s">
         <v>10</v>
@@ -6873,16 +6928,16 @@
         <v>3</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q52" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R52" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S52" s="12" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="53" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -6896,16 +6951,16 @@
         <v>9</v>
       </c>
       <c r="D53" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E53" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F53" s="4" t="s">
         <v>112</v>
       </c>
       <c r="G53" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H53" s="3" t="s">
         <v>21</v>
@@ -6938,13 +6993,13 @@
         <v>3</v>
       </c>
       <c r="P53" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q53" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R53" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S53" s="12" t="s">
         <v>9</v>
@@ -6955,22 +7010,22 @@
         <v>75</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E54" s="13">
         <v>183</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="G54" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H54" s="3" t="s">
         <v>30</v>
@@ -7003,16 +7058,16 @@
         <v>2</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q54" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R54" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S54" s="12" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
     </row>
     <row r="55" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -7020,19 +7075,19 @@
         <v>76</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D55" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E55" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="G55" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H55" s="3" t="s">
         <v>10</v>
@@ -7065,13 +7120,13 @@
         <v>2</v>
       </c>
       <c r="P55" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q55" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R55" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S55" s="12" t="s">
         <v>9</v>
@@ -7088,19 +7143,19 @@
         <v>115</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E56" s="13" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="G56" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H56" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I56" s="3">
         <f>VLOOKUP(H56,cardsort_group_IDs!A:B,2,0)</f>
@@ -7133,10 +7188,10 @@
         <v>93</v>
       </c>
       <c r="Q56" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R56" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S56" s="12" t="s">
         <v>9</v>
@@ -7153,16 +7208,16 @@
         <v>9</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E57" s="13" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F57" s="4" t="s">
         <v>117</v>
       </c>
       <c r="G57" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H57" s="3" t="s">
         <v>56</v>
@@ -7198,10 +7253,10 @@
         <v>93</v>
       </c>
       <c r="Q57" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R57" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S57" s="12" t="s">
         <v>9</v>
@@ -7227,7 +7282,7 @@
         <v>119</v>
       </c>
       <c r="G58" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H58" s="3" t="s">
         <v>56</v>
@@ -7237,7 +7292,7 @@
         <v>208</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="K58" s="3">
         <f>VLOOKUP(J58,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -7260,13 +7315,13 @@
         <v>1</v>
       </c>
       <c r="P58" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q58" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R58" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S58" s="12" t="s">
         <v>9</v>
@@ -7277,7 +7332,7 @@
         <v>82</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C59" s="4" t="s">
         <v>120</v>
@@ -7292,7 +7347,7 @@
         <v>121</v>
       </c>
       <c r="G59" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>10</v>
@@ -7325,13 +7380,13 @@
         <v>1</v>
       </c>
       <c r="P59" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q59" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R59" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S59" s="12" t="s">
         <v>9</v>
@@ -7345,22 +7400,22 @@
         <v>122</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="E60" s="13" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="F60" s="4" t="s">
         <v>123</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H60" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I60" s="3">
         <f>VLOOKUP(H60,cardsort_group_IDs!A:B,2,0)</f>
@@ -7393,13 +7448,13 @@
         <v>93</v>
       </c>
       <c r="Q60" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R60" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S60" s="12" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="61" spans="1:19" ht="90" x14ac:dyDescent="0.25">
@@ -7413,16 +7468,16 @@
         <v>9</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E61" s="13" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H61" s="3" t="s">
         <v>15</v>
@@ -7455,16 +7510,16 @@
         <v>5</v>
       </c>
       <c r="P61" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q61" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R61" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S61" s="12" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="62" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -7472,22 +7527,22 @@
         <v>88</v>
       </c>
       <c r="B62" s="3" t="s">
+        <v>715</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>716</v>
+      </c>
+      <c r="D62" s="10" t="s">
+        <v>575</v>
+      </c>
+      <c r="E62" s="13" t="s">
+        <v>287</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>717</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>718</v>
-      </c>
-      <c r="D62" s="10" t="s">
-        <v>577</v>
-      </c>
-      <c r="E62" s="13" t="s">
-        <v>288</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>719</v>
-      </c>
       <c r="G62" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H62" s="3" t="s">
         <v>30</v>
@@ -7520,13 +7575,13 @@
         <v>4</v>
       </c>
       <c r="P62" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q62" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R62" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S62" s="12" t="s">
         <v>9</v>
@@ -7540,19 +7595,19 @@
         <v>125</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E63" s="13" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H63" s="3" t="s">
         <v>30</v>
@@ -7585,13 +7640,13 @@
         <v>8</v>
       </c>
       <c r="P63" s="12" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="Q63" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R63" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S63" s="12" t="s">
         <v>9</v>
@@ -7605,19 +7660,19 @@
         <v>126</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E64" s="13" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H64" s="3" t="s">
         <v>30</v>
@@ -7653,10 +7708,10 @@
         <v>93</v>
       </c>
       <c r="Q64" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R64" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S64" s="12" t="s">
         <v>9</v>
@@ -7670,19 +7725,19 @@
         <v>127</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="E65" s="13" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F65" s="4" t="s">
         <v>128</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H65" s="3" t="s">
         <v>15</v>
@@ -7715,13 +7770,13 @@
         <v>4</v>
       </c>
       <c r="P65" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q65" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R65" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S65" s="12" t="s">
         <v>9</v>
@@ -7738,16 +7793,16 @@
         <v>9</v>
       </c>
       <c r="D66" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E66" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>130</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H66" s="3" t="s">
         <v>42</v>
@@ -7780,13 +7835,13 @@
         <v>3</v>
       </c>
       <c r="P66" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q66" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R66" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S66" s="12" t="s">
         <v>9</v>
@@ -7812,7 +7867,7 @@
         <v>132</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H67" s="3" t="s">
         <v>10</v>
@@ -7845,13 +7900,13 @@
         <v>1</v>
       </c>
       <c r="P67" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q67" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R67" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S67" s="12" t="s">
         <v>9</v>
@@ -7865,19 +7920,19 @@
         <v>133</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D68" s="12" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E68" s="13" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H68" s="3" t="s">
         <v>56</v>
@@ -7910,16 +7965,16 @@
         <v>4</v>
       </c>
       <c r="P68" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q68" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R68" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S68" s="12" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="69" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -7927,22 +7982,22 @@
         <v>95</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="D69" s="13" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E69" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H69" s="3" t="s">
         <v>21</v>
@@ -7975,16 +8030,16 @@
         <v>1</v>
       </c>
       <c r="P69" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q69" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R69" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S69" s="12" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
     </row>
     <row r="70" spans="1:19" x14ac:dyDescent="0.25">
@@ -8007,7 +8062,7 @@
         <v>135</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H70" s="3" t="s">
         <v>21</v>
@@ -8040,13 +8095,13 @@
         <v>1</v>
       </c>
       <c r="P70" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q70" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R70" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S70" s="12" t="s">
         <v>9</v>
@@ -8057,10 +8112,10 @@
         <v>98</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D71" s="10">
         <v>209</v>
@@ -8072,7 +8127,7 @@
         <v>136</v>
       </c>
       <c r="G71" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H71" s="3" t="s">
         <v>10</v>
@@ -8105,13 +8160,13 @@
         <v>2</v>
       </c>
       <c r="P71" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q71" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R71" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S71" s="12" t="s">
         <v>9</v>
@@ -8122,7 +8177,7 @@
         <v>99</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="C72" s="4" t="s">
         <v>9</v>
@@ -8134,10 +8189,10 @@
         <v>508</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="G72" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H72" s="3" t="s">
         <v>10</v>
@@ -8170,13 +8225,13 @@
         <v>1</v>
       </c>
       <c r="P72" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q72" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R72" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S72" s="12" t="s">
         <v>9</v>
@@ -8202,7 +8257,7 @@
         <v>138</v>
       </c>
       <c r="G73" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H73" s="3" t="s">
         <v>10</v>
@@ -8235,13 +8290,13 @@
         <v>1</v>
       </c>
       <c r="P73" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q73" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R73" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S73" s="12" t="s">
         <v>9</v>
@@ -8252,22 +8307,22 @@
         <v>102</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>139</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E74" s="13">
         <v>501</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="G74" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H74" s="3" t="s">
         <v>15</v>
@@ -8300,13 +8355,13 @@
         <v>3</v>
       </c>
       <c r="P74" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q74" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R74" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S74" s="12" t="s">
         <v>9</v>
@@ -8317,25 +8372,25 @@
         <v>104</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="C75" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D75" s="12" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E75" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="G75" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H75" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I75" s="3">
         <f>VLOOKUP(H75,cardsort_group_IDs!A:B,2,0)</f>
@@ -8365,13 +8420,13 @@
         <v>2</v>
       </c>
       <c r="P75" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q75" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R75" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S75" s="12" t="s">
         <v>9</v>
@@ -8388,16 +8443,16 @@
         <v>9</v>
       </c>
       <c r="D76" s="12" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E76" s="13" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="F76" s="4" t="s">
         <v>142</v>
       </c>
       <c r="G76" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H76" s="3" t="s">
         <v>15</v>
@@ -8430,13 +8485,13 @@
         <v>7</v>
       </c>
       <c r="P76" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q76" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R76" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S76" s="12" t="s">
         <v>9</v>
@@ -8447,22 +8502,22 @@
         <v>108</v>
       </c>
       <c r="B77" s="18" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E77" s="13" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F77" s="4" t="s">
         <v>143</v>
       </c>
       <c r="G77" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H77" s="3" t="s">
         <v>15</v>
@@ -8495,13 +8550,13 @@
         <v>8</v>
       </c>
       <c r="P77" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q77" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R77" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S77" s="12" t="s">
         <v>9</v>
@@ -8512,22 +8567,22 @@
         <v>109</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="D78" s="13" t="s">
+        <v>732</v>
+      </c>
+      <c r="E78" s="13" t="s">
+        <v>309</v>
+      </c>
+      <c r="F78" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="E78" s="13" t="s">
-        <v>310</v>
-      </c>
-      <c r="F78" s="4" t="s">
-        <v>736</v>
-      </c>
       <c r="G78" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H78" s="3" t="s">
         <v>21</v>
@@ -8560,16 +8615,16 @@
         <v>7</v>
       </c>
       <c r="P78" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q78" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R78" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S78" s="12" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
     </row>
     <row r="79" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -8586,16 +8641,16 @@
         <v>9</v>
       </c>
       <c r="E79" s="13" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H79" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I79" s="3">
         <f>VLOOKUP(H79,cardsort_group_IDs!A:B,2,0)</f>
@@ -8628,13 +8683,13 @@
         <v>93</v>
       </c>
       <c r="Q79" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R79" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S79" s="12" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
     </row>
     <row r="80" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -8642,25 +8697,25 @@
         <v>113</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D80" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E80" s="13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F80" s="5" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H80" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I80" s="3">
         <f>VLOOKUP(H80,cardsort_group_IDs!A:B,2,0)</f>
@@ -8693,13 +8748,13 @@
         <v>93</v>
       </c>
       <c r="Q80" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R80" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S80" s="12" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
     </row>
     <row r="81" spans="1:19" ht="150" x14ac:dyDescent="0.25">
@@ -8707,22 +8762,22 @@
         <v>114</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="D81" s="13" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="E81" s="13" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="G81" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H81" s="3" t="s">
         <v>46</v>
@@ -8732,7 +8787,7 @@
         <v>207</v>
       </c>
       <c r="J81" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="K81" s="3">
         <f>VLOOKUP(J81,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8758,10 +8813,10 @@
         <v>93</v>
       </c>
       <c r="Q81" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R81" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S81" s="12" t="s">
         <v>9</v>
@@ -8775,7 +8830,7 @@
         <v>146</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D82" s="12" t="s">
         <v>9</v>
@@ -8784,10 +8839,10 @@
         <v>183</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="G82" s="3" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="H82" s="3" t="s">
         <v>42</v>
@@ -8820,19 +8875,19 @@
         <v>1</v>
       </c>
       <c r="P82" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q82" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R82" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S82" s="12" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="83" spans="1:19" ht="45" x14ac:dyDescent="0.25">
+        <v>748</v>
+      </c>
+    </row>
+    <row r="83" spans="1:19" ht="60" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
         <v>116</v>
       </c>
@@ -8840,19 +8895,19 @@
         <v>147</v>
       </c>
       <c r="C83" s="4" t="s">
-        <v>751</v>
+        <v>853</v>
       </c>
       <c r="D83" s="12" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="E83" s="13" t="s">
-        <v>311</v>
+        <v>861</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>148</v>
+        <v>852</v>
       </c>
       <c r="G83" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H83" s="3" t="s">
         <v>30</v>
@@ -8862,7 +8917,7 @@
         <v>205</v>
       </c>
       <c r="J83" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K83" s="3">
         <f>VLOOKUP(J83,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -8878,23 +8933,23 @@
       </c>
       <c r="N83" s="3">
         <f t="shared" si="9"/>
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="O83" s="3">
         <f t="shared" si="7"/>
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P83" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q83" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R83" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S83" s="12" t="s">
-        <v>9</v>
+        <v>854</v>
       </c>
     </row>
     <row r="84" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -8905,19 +8960,19 @@
         <v>35</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="E84" s="13" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G84" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H84" s="3" t="s">
         <v>30</v>
@@ -8953,10 +9008,10 @@
         <v>93</v>
       </c>
       <c r="Q84" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R84" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S84" s="12" t="s">
         <v>9</v>
@@ -8967,7 +9022,7 @@
         <v>118</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C85" s="4" t="s">
         <v>9</v>
@@ -8979,10 +9034,10 @@
         <v>9</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G85" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H85" s="3" t="s">
         <v>21</v>
@@ -8992,7 +9047,7 @@
         <v>202</v>
       </c>
       <c r="J85" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="K85" s="3">
         <f>VLOOKUP(J85,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9015,13 +9070,13 @@
         <v>1</v>
       </c>
       <c r="P85" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q85" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R85" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S85" s="12" t="s">
         <v>9</v>
@@ -9032,22 +9087,22 @@
         <v>120</v>
       </c>
       <c r="B86" t="s">
+        <v>752</v>
+      </c>
+      <c r="C86" s="4" t="s">
         <v>755</v>
       </c>
-      <c r="C86" s="4" t="s">
-        <v>758</v>
-      </c>
       <c r="D86" s="12" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="E86" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="F86" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
       <c r="G86" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H86" s="3" t="s">
         <v>15</v>
@@ -9080,16 +9135,16 @@
         <v>3</v>
       </c>
       <c r="P86" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q86" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R86" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S86" s="12" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
     </row>
     <row r="87" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -9097,22 +9152,22 @@
         <v>121</v>
       </c>
       <c r="B87" s="27" t="s">
+        <v>153</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="D87" s="12" t="s">
+        <v>465</v>
+      </c>
+      <c r="E87" s="13" t="s">
+        <v>655</v>
+      </c>
+      <c r="F87" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="C87" s="4" t="s">
-        <v>176</v>
-      </c>
-      <c r="D87" s="12" t="s">
-        <v>467</v>
-      </c>
-      <c r="E87" s="13" t="s">
-        <v>657</v>
-      </c>
-      <c r="F87" s="4" t="s">
-        <v>155</v>
-      </c>
       <c r="G87" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H87" s="3" t="s">
         <v>15</v>
@@ -9148,10 +9203,10 @@
         <v>93</v>
       </c>
       <c r="Q87" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R87" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S87" s="12" t="s">
         <v>9</v>
@@ -9162,22 +9217,22 @@
         <v>122</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E88" s="13" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="G88" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H88" s="3" t="s">
         <v>15</v>
@@ -9213,13 +9268,13 @@
         <v>93</v>
       </c>
       <c r="Q88" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R88" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S88" s="12" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="89" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -9227,25 +9282,25 @@
         <v>124</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D89" s="12" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="E89" s="13" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="G89" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H89" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I89" s="3">
         <f>VLOOKUP(H89,cardsort_group_IDs!A:B,2,0)</f>
@@ -9275,16 +9330,16 @@
         <v>9</v>
       </c>
       <c r="P89" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q89" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R89" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S89" s="12" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="90" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9292,22 +9347,22 @@
         <v>126</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C90" s="4" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E90" s="13">
         <v>501</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="G90" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H90" s="3" t="s">
         <v>46</v>
@@ -9317,7 +9372,7 @@
         <v>207</v>
       </c>
       <c r="J90" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="K90" s="3">
         <f>VLOOKUP(J90,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9340,13 +9395,13 @@
         <v>2</v>
       </c>
       <c r="P90" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q90" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R90" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S90" s="12" t="s">
         <v>9</v>
@@ -9357,22 +9412,22 @@
         <v>127</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
       <c r="D91" s="12" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="E91" s="13" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="G91" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H91" s="3" t="s">
         <v>46</v>
@@ -9382,7 +9437,7 @@
         <v>207</v>
       </c>
       <c r="J91" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="K91" s="3">
         <f>VLOOKUP(J91,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9405,16 +9460,16 @@
         <v>4</v>
       </c>
       <c r="P91" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q91" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R91" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S91" s="12" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
     </row>
     <row r="92" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9422,22 +9477,22 @@
         <v>128</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E92" s="13">
         <v>501</v>
       </c>
       <c r="F92" s="5" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="G92" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H92" s="3" t="s">
         <v>46</v>
@@ -9447,7 +9502,7 @@
         <v>207</v>
       </c>
       <c r="J92" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="K92" s="3">
         <f>VLOOKUP(J92,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9470,13 +9525,13 @@
         <v>2</v>
       </c>
       <c r="P92" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q92" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R92" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S92" s="12" t="s">
         <v>9</v>
@@ -9487,22 +9542,22 @@
         <v>129</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="C93" s="4" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D93" s="12" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="E93" s="13" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="G93" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H93" s="3" t="s">
         <v>46</v>
@@ -9512,7 +9567,7 @@
         <v>207</v>
       </c>
       <c r="J93" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="K93" s="3">
         <f>VLOOKUP(J93,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -9538,10 +9593,10 @@
         <v>93</v>
       </c>
       <c r="Q93" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R93" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S93" s="12" t="s">
         <v>9</v>
@@ -9552,25 +9607,25 @@
         <v>130</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="C94" s="4" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="D94" s="12" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="E94" s="13" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="G94" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H94" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I94" s="3">
         <f>VLOOKUP(H94,cardsort_group_IDs!A:B,2,0)</f>
@@ -9600,13 +9655,13 @@
         <v>5</v>
       </c>
       <c r="P94" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q94" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R94" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S94" s="12" t="s">
         <v>9</v>
@@ -9617,22 +9672,22 @@
         <v>133</v>
       </c>
       <c r="B95" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>765</v>
+      </c>
+      <c r="D95" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E95" s="13" t="s">
+        <v>766</v>
+      </c>
+      <c r="F95" s="4" t="s">
         <v>767</v>
       </c>
-      <c r="C95" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="D95" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E95" s="13" t="s">
-        <v>769</v>
-      </c>
-      <c r="F95" s="4" t="s">
-        <v>770</v>
-      </c>
       <c r="G95" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H95" s="3" t="s">
         <v>30</v>
@@ -9668,13 +9723,13 @@
         <v>93</v>
       </c>
       <c r="Q95" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R95" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S95" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
     </row>
     <row r="96" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9682,7 +9737,7 @@
         <v>134</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="C96" s="4" t="s">
         <v>9</v>
@@ -9691,13 +9746,13 @@
         <v>9</v>
       </c>
       <c r="E96" s="13" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="G96" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H96" s="3" t="s">
         <v>30</v>
@@ -9733,13 +9788,13 @@
         <v>93</v>
       </c>
       <c r="Q96" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R96" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S96" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="97" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -9747,7 +9802,7 @@
         <v>135</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C97" s="4" t="s">
         <v>9</v>
@@ -9759,13 +9814,13 @@
         <v>183</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="G97" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H97" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I97" s="3">
         <f>VLOOKUP(H97,cardsort_group_IDs!A:B,2,0)</f>
@@ -9795,13 +9850,13 @@
         <v>1</v>
       </c>
       <c r="P97" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q97" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R97" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S97" s="12" t="s">
         <v>9</v>
@@ -9812,25 +9867,25 @@
         <v>137</v>
       </c>
       <c r="B98" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="C98" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C98" s="4" t="s">
+      <c r="D98" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E98" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="D98" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E98" s="29" t="s">
-        <v>173</v>
-      </c>
       <c r="F98" s="4" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="G98" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H98" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I98" s="3">
         <f>VLOOKUP(H98,cardsort_group_IDs!A:B,2,0)</f>
@@ -9860,13 +9915,13 @@
         <v>6</v>
       </c>
       <c r="P98" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q98" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R98" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S98" s="12" t="s">
         <v>9</v>
@@ -9877,10 +9932,10 @@
         <v>138</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="C99" s="4" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="D99" s="12" t="s">
         <v>9</v>
@@ -9889,10 +9944,10 @@
         <v>236</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="G99" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H99" t="s">
         <v>10</v>
@@ -9925,13 +9980,13 @@
         <v>1</v>
       </c>
       <c r="P99" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q99" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R99" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S99" s="12" t="s">
         <v>9</v>
@@ -9942,7 +9997,7 @@
         <v>139</v>
       </c>
       <c r="B100" s="18" t="s">
-        <v>391</v>
+        <v>389</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>9</v>
@@ -9954,10 +10009,10 @@
         <v>9</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G100" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H100" s="3" t="s">
         <v>21</v>
@@ -9990,13 +10045,13 @@
         <v>1</v>
       </c>
       <c r="P100" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q100" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R100" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S100" s="12" t="s">
         <v>9</v>
@@ -10007,22 +10062,22 @@
         <v>140</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C101" s="4" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="D101" s="12" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="E101" s="13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="G101" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H101" s="3" t="s">
         <v>15</v>
@@ -10055,13 +10110,13 @@
         <v>18</v>
       </c>
       <c r="P101" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q101" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R101" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S101" s="12">
         <v>2</v>
@@ -10072,22 +10127,22 @@
         <v>141</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D102" s="12" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E102" s="13" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="G102" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H102" s="3" t="s">
         <v>46</v>
@@ -10097,7 +10152,7 @@
         <v>207</v>
       </c>
       <c r="J102" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="K102" s="3">
         <f>VLOOKUP(J102,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10120,13 +10175,13 @@
         <v>4</v>
       </c>
       <c r="P102" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q102" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R102" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S102" s="12">
         <v>129</v>
@@ -10137,22 +10192,22 @@
         <v>142</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D103" s="12" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="E103" s="13" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="G103" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H103" s="3" t="s">
         <v>46</v>
@@ -10162,7 +10217,7 @@
         <v>207</v>
       </c>
       <c r="J103" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="K103" s="3">
         <f>VLOOKUP(J103,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10185,13 +10240,13 @@
         <v>3</v>
       </c>
       <c r="P103" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q103" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R103" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S103" s="12">
         <v>19</v>
@@ -10202,22 +10257,22 @@
         <v>143</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="E104" s="13" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="G104" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H104" s="3" t="s">
         <v>46</v>
@@ -10227,7 +10282,7 @@
         <v>207</v>
       </c>
       <c r="J104" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="K104" s="3">
         <f>VLOOKUP(J104,cardsort_subgroup_IDs!A:B,2,0)</f>
@@ -10250,13 +10305,13 @@
         <v>6</v>
       </c>
       <c r="P104" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q104" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R104" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S104" s="12" t="s">
         <v>9</v>
@@ -10267,22 +10322,22 @@
         <v>144</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C105" s="4" t="s">
         <v>9</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E105" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="G105" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H105" s="3" t="s">
         <v>15</v>
@@ -10315,16 +10370,16 @@
         <v>1</v>
       </c>
       <c r="P105" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q105" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R105" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S105" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="106" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10332,22 +10387,22 @@
         <v>145</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C106" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="E106" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="G106" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H106" t="s">
         <v>10</v>
@@ -10380,16 +10435,16 @@
         <v>1</v>
       </c>
       <c r="P106" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q106" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R106" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S106" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="107" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10397,22 +10452,22 @@
         <v>146</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="C107" s="4" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="D107" t="s">
+        <v>445</v>
+      </c>
+      <c r="E107" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="F107" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="E107" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="F107" s="4" t="s">
-        <v>449</v>
-      </c>
       <c r="G107" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H107" t="s">
         <v>10</v>
@@ -10445,16 +10500,16 @@
         <v>6</v>
       </c>
       <c r="P107" s="12" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="Q107" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R107" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S107" s="12" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
     </row>
     <row r="108" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -10462,22 +10517,22 @@
         <v>147</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="E108" s="13" t="s">
         <v>9</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="G108" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H108" s="3" t="s">
         <v>15</v>
@@ -10510,16 +10565,16 @@
         <v>1</v>
       </c>
       <c r="P108" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="Q108" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R108" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S108" s="12" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
     </row>
     <row r="109" spans="1:19" x14ac:dyDescent="0.25">
@@ -10527,22 +10582,22 @@
         <v>148</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C109" s="4" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D109" t="s">
+        <v>473</v>
+      </c>
+      <c r="E109" s="13" t="s">
         <v>475</v>
       </c>
-      <c r="E109" s="13" t="s">
-        <v>477</v>
-      </c>
       <c r="F109" s="4" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="G109" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H109" s="3" t="s">
         <v>10</v>
@@ -10578,13 +10633,13 @@
         <v>93</v>
       </c>
       <c r="Q109" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R109" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S109" s="12" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
     </row>
     <row r="110" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -10592,22 +10647,22 @@
         <v>149</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C110" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="D110" s="12" t="s">
+        <v>466</v>
+      </c>
+      <c r="E110" s="13" t="s">
+        <v>475</v>
+      </c>
+      <c r="F110" s="4" t="s">
         <v>793</v>
       </c>
-      <c r="D110" s="12" t="s">
-        <v>468</v>
-      </c>
-      <c r="E110" s="13" t="s">
-        <v>477</v>
-      </c>
-      <c r="F110" s="4" t="s">
-        <v>796</v>
-      </c>
       <c r="G110" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H110" s="3" t="s">
         <v>21</v>
@@ -10643,13 +10698,13 @@
         <v>93</v>
       </c>
       <c r="Q110" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R110" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S110" s="12" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
     </row>
     <row r="111" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -10657,25 +10712,25 @@
         <v>150</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C111" s="4" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E111" s="13" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="G111" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H111" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I111" s="3">
         <f>VLOOKUP(H111,cardsort_group_IDs!A:B,2,0)</f>
@@ -10708,13 +10763,13 @@
         <v>93</v>
       </c>
       <c r="Q111" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R111" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S111" s="12" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
     </row>
     <row r="112" spans="1:19" x14ac:dyDescent="0.25">
@@ -10722,7 +10777,7 @@
         <v>151</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="C112" s="4" t="s">
         <v>9</v>
@@ -10731,13 +10786,13 @@
         <v>9</v>
       </c>
       <c r="E112" s="13" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G112" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H112" s="3" t="s">
         <v>15</v>
@@ -10773,10 +10828,10 @@
         <v>93</v>
       </c>
       <c r="Q112" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R112" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S112" s="12" t="s">
         <v>9</v>
@@ -10787,7 +10842,7 @@
         <v>152</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C113" s="4" t="s">
         <v>9</v>
@@ -10796,16 +10851,16 @@
         <v>9</v>
       </c>
       <c r="E113" s="13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="G113" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H113" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I113" s="3">
         <f>VLOOKUP(H113,cardsort_group_IDs!A:B,2,0)</f>
@@ -10838,10 +10893,10 @@
         <v>93</v>
       </c>
       <c r="Q113" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R113" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S113" s="12" t="s">
         <v>9</v>
@@ -10852,7 +10907,7 @@
         <v>153</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="C114" s="4" t="s">
         <v>9</v>
@@ -10861,16 +10916,16 @@
         <v>9</v>
       </c>
       <c r="E114" s="13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="G114" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H114" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I114" s="3">
         <f>VLOOKUP(H114,cardsort_group_IDs!A:B,2,0)</f>
@@ -10903,13 +10958,13 @@
         <v>93</v>
       </c>
       <c r="Q114" s="12" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="R114" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S114" s="12" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
     </row>
     <row r="115" spans="1:19" x14ac:dyDescent="0.25">
@@ -10917,25 +10972,25 @@
         <v>154</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C115" s="4" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D115" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E115" s="13" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="G115" s="3" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="H115" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I115" s="3">
         <f>VLOOKUP(H115,cardsort_group_IDs!A:B,2,0)</f>
@@ -10968,13 +11023,13 @@
         <v>93</v>
       </c>
       <c r="Q115" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R115" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S115" s="12" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
     </row>
     <row r="116" spans="1:19" ht="105" x14ac:dyDescent="0.25">
@@ -10982,25 +11037,25 @@
         <v>155</v>
       </c>
       <c r="B116" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="C116" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D116" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E116" s="13" t="s">
         <v>533</v>
       </c>
-      <c r="C116" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D116" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E116" s="13" t="s">
-        <v>535</v>
-      </c>
       <c r="F116" s="4" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="G116" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H116" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I116" s="3">
         <f>VLOOKUP(H116,cardsort_group_IDs!A:B,2,0)</f>
@@ -11030,16 +11085,16 @@
         <v>2</v>
       </c>
       <c r="P116" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q116" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R116" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S116" s="12" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
     </row>
     <row r="117" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11047,22 +11102,22 @@
         <v>156</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="C117" s="4" t="s">
+        <v>535</v>
+      </c>
+      <c r="D117" s="12" t="s">
+        <v>538</v>
+      </c>
+      <c r="E117" s="13" t="s">
+        <v>539</v>
+      </c>
+      <c r="F117" s="4" t="s">
         <v>537</v>
       </c>
-      <c r="D117" s="12" t="s">
-        <v>540</v>
-      </c>
-      <c r="E117" s="13" t="s">
-        <v>541</v>
-      </c>
-      <c r="F117" s="4" t="s">
-        <v>539</v>
-      </c>
       <c r="G117" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H117" s="3" t="s">
         <v>30</v>
@@ -11095,13 +11150,13 @@
         <v>2</v>
       </c>
       <c r="P117" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q117" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R117" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="S117" s="12" t="s">
         <v>9</v>
@@ -11112,25 +11167,25 @@
         <v>157</v>
       </c>
       <c r="B118" s="3" t="s">
+        <v>543</v>
+      </c>
+      <c r="C118" t="s">
+        <v>544</v>
+      </c>
+      <c r="D118" s="12" t="s">
+        <v>556</v>
+      </c>
+      <c r="E118" s="13" t="s">
+        <v>546</v>
+      </c>
+      <c r="F118" s="4" t="s">
         <v>545</v>
       </c>
-      <c r="C118" t="s">
-        <v>546</v>
-      </c>
-      <c r="D118" s="12" t="s">
-        <v>558</v>
-      </c>
-      <c r="E118" s="13" t="s">
-        <v>548</v>
-      </c>
-      <c r="F118" s="4" t="s">
-        <v>547</v>
-      </c>
       <c r="G118" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H118" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I118" s="3">
         <f>VLOOKUP(H118,cardsort_group_IDs!A:B,2,0)</f>
@@ -11160,16 +11215,16 @@
         <v>5</v>
       </c>
       <c r="P118" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q118" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R118" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S118" s="12" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
     </row>
     <row r="119" spans="1:19" ht="30" x14ac:dyDescent="0.25">
@@ -11177,10 +11232,10 @@
         <v>158</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="C119" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D119" s="12" t="s">
         <v>9</v>
@@ -11189,10 +11244,10 @@
         <v>505</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="G119" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H119" s="3" t="s">
         <v>30</v>
@@ -11225,13 +11280,13 @@
         <v>1</v>
       </c>
       <c r="P119" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q119" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R119" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S119" s="12" t="s">
         <v>9</v>
@@ -11242,22 +11297,22 @@
         <v>159</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="C120" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D120" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E120" s="13" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="G120" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H120" s="3" t="s">
         <v>15</v>
@@ -11290,16 +11345,16 @@
         <v>2</v>
       </c>
       <c r="P120" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q120" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R120" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="S120" s="12" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
     </row>
     <row r="121" spans="1:19" ht="75" x14ac:dyDescent="0.25">
@@ -11307,22 +11362,22 @@
         <v>160</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C121" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="D121" s="12" t="s">
         <v>9</v>
       </c>
       <c r="E121" s="13" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="G121" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H121" s="3" t="s">
         <v>15</v>
@@ -11355,16 +11410,16 @@
         <v>2</v>
       </c>
       <c r="P121" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q121" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R121" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S121" s="12" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
     </row>
     <row r="122" spans="1:19" ht="45" x14ac:dyDescent="0.25">
@@ -11372,22 +11427,22 @@
         <v>161</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C122" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="D122" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E122" s="13" t="s">
+        <v>673</v>
+      </c>
+      <c r="F122" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="D122" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E122" s="13" t="s">
-        <v>675</v>
-      </c>
-      <c r="F122" s="4" t="s">
-        <v>676</v>
-      </c>
       <c r="G122" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H122" s="3" t="s">
         <v>15</v>
@@ -11412,24 +11467,24 @@
         <v>0</v>
       </c>
       <c r="N122" s="3">
-        <f t="shared" ref="N122:N123" si="53">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
+        <f t="shared" ref="N122:N124" si="53">IF(E122="-",0,LEN(E122)-LEN(SUBSTITUTE(E122,";",""))+1)</f>
         <v>2</v>
       </c>
       <c r="O122" s="3">
-        <f t="shared" ref="O122:O123" si="54">SUM(M122:N122)</f>
+        <f t="shared" ref="O122:O124" si="54">SUM(M122:N122)</f>
         <v>2</v>
       </c>
       <c r="P122" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q122" s="12" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="R122" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="S122" s="12" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
     </row>
     <row r="123" spans="1:19" ht="60" x14ac:dyDescent="0.25">
@@ -11437,7 +11492,7 @@
         <v>162</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C123" s="4" t="s">
         <v>9</v>
@@ -11446,16 +11501,16 @@
         <v>9</v>
       </c>
       <c r="E123" s="13" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="G123" s="3" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="H123" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="I123" s="3">
         <f>VLOOKUP(H123,cardsort_group_IDs!A:B,2,0)</f>
@@ -11469,11 +11524,11 @@
         <v>307</v>
       </c>
       <c r="L123" s="3">
-        <f t="shared" ref="L123" si="55">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
+        <f t="shared" ref="L123:L124" si="55">IF(E123="-",0,1)+IF(D123="-",0,2)</f>
         <v>1</v>
       </c>
       <c r="M123" s="3">
-        <f t="shared" ref="M123" si="56">IF(D123="-",0,LEN(D123)-LEN(SUBSTITUTE(D123,";",""))+1)</f>
+        <f t="shared" ref="M123:M124" si="56">IF(D123="-",0,LEN(D123)-LEN(SUBSTITUTE(D123,";",""))+1)</f>
         <v>0</v>
       </c>
       <c r="N123" s="3">
@@ -11485,17 +11540,121 @@
         <v>1</v>
       </c>
       <c r="P123" s="12" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="Q123" s="12" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="R123" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="S123" s="12" t="s">
-        <v>829</v>
-      </c>
+        <v>826</v>
+      </c>
+    </row>
+    <row r="124" spans="1:19" ht="30" x14ac:dyDescent="0.25">
+      <c r="A124" s="3">
+        <v>163</v>
+      </c>
+      <c r="B124" s="31" t="s">
+        <v>855</v>
+      </c>
+      <c r="C124" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="D124" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="E124" s="13" t="s">
+        <v>864</v>
+      </c>
+      <c r="F124" s="3" t="s">
+        <v>871</v>
+      </c>
+      <c r="G124" s="3" t="s">
+        <v>516</v>
+      </c>
+      <c r="H124" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="I124" s="3">
+        <f>VLOOKUP(H124,cardsort_group_IDs!A:B,2,0)</f>
+        <v>203</v>
+      </c>
+      <c r="J124" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="K124" s="3">
+        <f>VLOOKUP(J124,cardsort_subgroup_IDs!A:B,2,0)</f>
+        <v>313</v>
+      </c>
+      <c r="L124" s="3">
+        <f t="shared" si="55"/>
+        <v>1</v>
+      </c>
+      <c r="M124" s="3">
+        <f t="shared" si="56"/>
+        <v>0</v>
+      </c>
+      <c r="N124" s="3">
+        <f t="shared" si="53"/>
+        <v>2</v>
+      </c>
+      <c r="O124" s="3">
+        <f t="shared" si="54"/>
+        <v>2</v>
+      </c>
+      <c r="P124" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q124" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="R124" t="s">
+        <v>825</v>
+      </c>
+      <c r="S124" s="12" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="125" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B125" s="31"/>
+    </row>
+    <row r="126" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B126" s="31"/>
+    </row>
+    <row r="127" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B127" s="31"/>
+    </row>
+    <row r="128" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="B128" s="31"/>
+    </row>
+    <row r="129" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B129" s="31"/>
+    </row>
+    <row r="130" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B130" s="31"/>
+    </row>
+    <row r="131" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B131" s="31"/>
+    </row>
+    <row r="132" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B132" s="31"/>
+    </row>
+    <row r="133" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B133" s="31"/>
+    </row>
+    <row r="134" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B134" s="31"/>
+    </row>
+    <row r="135" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B135" s="31"/>
+    </row>
+    <row r="136" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B136" s="31"/>
+    </row>
+    <row r="137" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B137" s="31"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M123" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
@@ -11613,7 +11772,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{854C4F88-AAAD-435E-8324-B99D91D004B9}">
-  <dimension ref="A1:D153"/>
+  <dimension ref="A1:E157"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="9.140625" style="10"/>
@@ -11624,16 +11783,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="B1" t="s">
         <v>278</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
+        <v>489</v>
+      </c>
+      <c r="D1" s="8" t="s">
         <v>279</v>
-      </c>
-      <c r="C1" t="s">
-        <v>491</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -11641,13 +11800,13 @@
         <v>5</v>
       </c>
       <c r="B2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D2" t="s">
         <v>177</v>
-      </c>
-      <c r="C2" t="s">
-        <v>501</v>
-      </c>
-      <c r="D2" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -11655,27 +11814,27 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
+        <v>178</v>
+      </c>
+      <c r="C3" t="s">
+        <v>499</v>
+      </c>
+      <c r="D3" t="s">
         <v>179</v>
-      </c>
-      <c r="C3" t="s">
-        <v>501</v>
-      </c>
-      <c r="D3" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B4" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C4" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -11683,13 +11842,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
+        <v>180</v>
+      </c>
+      <c r="C5" t="s">
+        <v>499</v>
+      </c>
+      <c r="D5" t="s">
         <v>181</v>
-      </c>
-      <c r="C5" t="s">
-        <v>501</v>
-      </c>
-      <c r="D5" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -11697,13 +11856,13 @@
         <v>9</v>
       </c>
       <c r="B6" t="s">
+        <v>182</v>
+      </c>
+      <c r="C6" t="s">
+        <v>499</v>
+      </c>
+      <c r="D6" s="8" t="s">
         <v>183</v>
-      </c>
-      <c r="C6" t="s">
-        <v>501</v>
-      </c>
-      <c r="D6" s="8" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -11711,13 +11870,13 @@
         <v>11</v>
       </c>
       <c r="B7" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" t="s">
+        <v>499</v>
+      </c>
+      <c r="D7" s="8" t="s">
         <v>185</v>
-      </c>
-      <c r="C7" t="s">
-        <v>501</v>
-      </c>
-      <c r="D7" s="8" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -11725,13 +11884,13 @@
         <v>13</v>
       </c>
       <c r="B8" t="s">
+        <v>186</v>
+      </c>
+      <c r="C8" t="s">
+        <v>499</v>
+      </c>
+      <c r="D8" s="8" t="s">
         <v>187</v>
-      </c>
-      <c r="C8" t="s">
-        <v>501</v>
-      </c>
-      <c r="D8" s="8" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -11739,13 +11898,13 @@
         <v>14</v>
       </c>
       <c r="B9" t="s">
+        <v>188</v>
+      </c>
+      <c r="C9" t="s">
+        <v>499</v>
+      </c>
+      <c r="D9" s="8" t="s">
         <v>189</v>
-      </c>
-      <c r="C9" t="s">
-        <v>501</v>
-      </c>
-      <c r="D9" s="8" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -11753,13 +11912,13 @@
         <v>15</v>
       </c>
       <c r="B10" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="8" t="s">
         <v>191</v>
-      </c>
-      <c r="C10" t="s">
-        <v>501</v>
-      </c>
-      <c r="D10" s="8" t="s">
-        <v>192</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
@@ -11767,13 +11926,13 @@
         <v>17</v>
       </c>
       <c r="B11" t="s">
+        <v>192</v>
+      </c>
+      <c r="C11" t="s">
+        <v>499</v>
+      </c>
+      <c r="D11" s="8" t="s">
         <v>193</v>
-      </c>
-      <c r="C11" t="s">
-        <v>501</v>
-      </c>
-      <c r="D11" s="8" t="s">
-        <v>194</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -11781,13 +11940,13 @@
         <v>19</v>
       </c>
       <c r="B12" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="C12" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D12" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -11795,13 +11954,13 @@
         <v>20</v>
       </c>
       <c r="B13" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" t="s">
+        <v>499</v>
+      </c>
+      <c r="D13" s="8" t="s">
         <v>195</v>
-      </c>
-      <c r="C13" t="s">
-        <v>501</v>
-      </c>
-      <c r="D13" s="8" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -11809,13 +11968,13 @@
         <v>21</v>
       </c>
       <c r="B14" t="s">
+        <v>196</v>
+      </c>
+      <c r="C14" t="s">
+        <v>499</v>
+      </c>
+      <c r="D14" s="8" t="s">
         <v>197</v>
-      </c>
-      <c r="C14" t="s">
-        <v>501</v>
-      </c>
-      <c r="D14" s="8" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -11823,13 +11982,13 @@
         <v>31</v>
       </c>
       <c r="B15" t="s">
+        <v>198</v>
+      </c>
+      <c r="C15" t="s">
+        <v>499</v>
+      </c>
+      <c r="D15" s="8" t="s">
         <v>199</v>
-      </c>
-      <c r="C15" t="s">
-        <v>501</v>
-      </c>
-      <c r="D15" s="8" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -11837,13 +11996,13 @@
         <v>32</v>
       </c>
       <c r="B16" t="s">
+        <v>200</v>
+      </c>
+      <c r="C16" t="s">
+        <v>499</v>
+      </c>
+      <c r="D16" s="8" t="s">
         <v>201</v>
-      </c>
-      <c r="C16" t="s">
-        <v>501</v>
-      </c>
-      <c r="D16" s="8" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -11851,13 +12010,13 @@
         <v>36</v>
       </c>
       <c r="B17" t="s">
+        <v>202</v>
+      </c>
+      <c r="C17" t="s">
+        <v>499</v>
+      </c>
+      <c r="D17" s="8" t="s">
         <v>203</v>
-      </c>
-      <c r="C17" t="s">
-        <v>501</v>
-      </c>
-      <c r="D17" s="8" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.25">
@@ -11865,13 +12024,13 @@
         <v>39</v>
       </c>
       <c r="B18" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="C18" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D18" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -11879,13 +12038,13 @@
         <v>43</v>
       </c>
       <c r="B19" t="s">
+        <v>204</v>
+      </c>
+      <c r="C19" t="s">
+        <v>499</v>
+      </c>
+      <c r="D19" s="8" t="s">
         <v>205</v>
-      </c>
-      <c r="C19" t="s">
-        <v>501</v>
-      </c>
-      <c r="D19" s="8" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -11893,13 +12052,13 @@
         <v>45</v>
       </c>
       <c r="B20" t="s">
+        <v>206</v>
+      </c>
+      <c r="C20" t="s">
+        <v>499</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>207</v>
-      </c>
-      <c r="C20" t="s">
-        <v>501</v>
-      </c>
-      <c r="D20" s="8" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -11907,13 +12066,13 @@
         <v>46</v>
       </c>
       <c r="B21" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" t="s">
+        <v>499</v>
+      </c>
+      <c r="D21" s="8" t="s">
         <v>209</v>
-      </c>
-      <c r="C21" t="s">
-        <v>501</v>
-      </c>
-      <c r="D21" s="8" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -11921,13 +12080,13 @@
         <v>47</v>
       </c>
       <c r="B22" t="s">
+        <v>210</v>
+      </c>
+      <c r="C22" t="s">
+        <v>499</v>
+      </c>
+      <c r="D22" s="8" t="s">
         <v>211</v>
-      </c>
-      <c r="C22" t="s">
-        <v>501</v>
-      </c>
-      <c r="D22" s="8" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -11935,13 +12094,13 @@
         <v>49</v>
       </c>
       <c r="B23" t="s">
+        <v>212</v>
+      </c>
+      <c r="C23" t="s">
+        <v>499</v>
+      </c>
+      <c r="D23" s="8" t="s">
         <v>213</v>
-      </c>
-      <c r="C23" t="s">
-        <v>501</v>
-      </c>
-      <c r="D23" s="8" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -11949,13 +12108,13 @@
         <v>50</v>
       </c>
       <c r="B24" t="s">
+        <v>214</v>
+      </c>
+      <c r="C24" t="s">
+        <v>499</v>
+      </c>
+      <c r="D24" s="8" t="s">
         <v>215</v>
-      </c>
-      <c r="C24" t="s">
-        <v>501</v>
-      </c>
-      <c r="D24" s="8" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.25">
@@ -11963,13 +12122,13 @@
         <v>51</v>
       </c>
       <c r="B25" t="s">
+        <v>216</v>
+      </c>
+      <c r="C25" t="s">
+        <v>499</v>
+      </c>
+      <c r="D25" s="8" t="s">
         <v>217</v>
-      </c>
-      <c r="C25" t="s">
-        <v>501</v>
-      </c>
-      <c r="D25" s="8" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.25">
@@ -11977,13 +12136,13 @@
         <v>52</v>
       </c>
       <c r="B26" t="s">
+        <v>218</v>
+      </c>
+      <c r="C26" t="s">
+        <v>499</v>
+      </c>
+      <c r="D26" s="8" t="s">
         <v>219</v>
-      </c>
-      <c r="C26" t="s">
-        <v>501</v>
-      </c>
-      <c r="D26" s="8" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.25">
@@ -11991,13 +12150,13 @@
         <v>57</v>
       </c>
       <c r="B27" t="s">
+        <v>220</v>
+      </c>
+      <c r="C27" t="s">
+        <v>499</v>
+      </c>
+      <c r="D27" s="8" t="s">
         <v>221</v>
-      </c>
-      <c r="C27" t="s">
-        <v>501</v>
-      </c>
-      <c r="D27" s="8" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.25">
@@ -12005,13 +12164,13 @@
         <v>62</v>
       </c>
       <c r="B28" t="s">
+        <v>222</v>
+      </c>
+      <c r="C28" t="s">
+        <v>499</v>
+      </c>
+      <c r="D28" s="8" t="s">
         <v>223</v>
-      </c>
-      <c r="C28" t="s">
-        <v>501</v>
-      </c>
-      <c r="D28" s="8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.25">
@@ -12019,13 +12178,13 @@
         <v>70</v>
       </c>
       <c r="B29" t="s">
+        <v>224</v>
+      </c>
+      <c r="C29" t="s">
+        <v>499</v>
+      </c>
+      <c r="D29" s="8" t="s">
         <v>225</v>
-      </c>
-      <c r="C29" t="s">
-        <v>501</v>
-      </c>
-      <c r="D29" s="8" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.25">
@@ -12033,13 +12192,13 @@
         <v>87</v>
       </c>
       <c r="B30" t="s">
+        <v>226</v>
+      </c>
+      <c r="C30" t="s">
+        <v>499</v>
+      </c>
+      <c r="D30" s="8" t="s">
         <v>227</v>
-      </c>
-      <c r="C30" t="s">
-        <v>501</v>
-      </c>
-      <c r="D30" s="8" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.25">
@@ -12047,13 +12206,13 @@
         <v>92</v>
       </c>
       <c r="B31" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="C31" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D31" s="8" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:4" ht="75" x14ac:dyDescent="0.25">
@@ -12061,13 +12220,13 @@
         <v>96</v>
       </c>
       <c r="B32" t="s">
+        <v>229</v>
+      </c>
+      <c r="C32" t="s">
+        <v>499</v>
+      </c>
+      <c r="D32" s="8" t="s">
         <v>230</v>
-      </c>
-      <c r="C32" t="s">
-        <v>501</v>
-      </c>
-      <c r="D32" s="8" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.25">
@@ -12075,13 +12234,13 @@
         <v>101</v>
       </c>
       <c r="B33" t="s">
+        <v>231</v>
+      </c>
+      <c r="C33" t="s">
+        <v>499</v>
+      </c>
+      <c r="D33" s="8" t="s">
         <v>232</v>
-      </c>
-      <c r="C33" t="s">
-        <v>501</v>
-      </c>
-      <c r="D33" s="8" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="34" spans="1:4" ht="60" x14ac:dyDescent="0.25">
@@ -12089,13 +12248,13 @@
         <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="C34" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D34" s="17" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.25">
@@ -12103,13 +12262,13 @@
         <v>108</v>
       </c>
       <c r="B35" t="s">
+        <v>233</v>
+      </c>
+      <c r="C35" t="s">
+        <v>499</v>
+      </c>
+      <c r="D35" s="8" t="s">
         <v>234</v>
-      </c>
-      <c r="C35" t="s">
-        <v>501</v>
-      </c>
-      <c r="D35" s="8" t="s">
-        <v>235</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.25">
@@ -12117,13 +12276,13 @@
         <v>111</v>
       </c>
       <c r="B36" t="s">
+        <v>235</v>
+      </c>
+      <c r="C36" t="s">
+        <v>499</v>
+      </c>
+      <c r="D36" s="8" t="s">
         <v>236</v>
-      </c>
-      <c r="C36" t="s">
-        <v>501</v>
-      </c>
-      <c r="D36" s="8" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.25">
@@ -12131,13 +12290,13 @@
         <v>115</v>
       </c>
       <c r="B37" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" t="s">
+        <v>499</v>
+      </c>
+      <c r="D37" s="8" t="s">
         <v>238</v>
-      </c>
-      <c r="C37" t="s">
-        <v>501</v>
-      </c>
-      <c r="D37" s="8" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.25">
@@ -12145,13 +12304,13 @@
         <v>131</v>
       </c>
       <c r="B38" t="s">
+        <v>240</v>
+      </c>
+      <c r="C38" t="s">
+        <v>499</v>
+      </c>
+      <c r="D38" s="17" t="s">
         <v>241</v>
-      </c>
-      <c r="C38" t="s">
-        <v>501</v>
-      </c>
-      <c r="D38" s="17" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="39" spans="1:4" s="9" customFormat="1" x14ac:dyDescent="0.25">
@@ -12159,13 +12318,13 @@
         <v>146</v>
       </c>
       <c r="B39" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" t="s">
+        <v>499</v>
+      </c>
+      <c r="D39" s="8" t="s">
         <v>243</v>
-      </c>
-      <c r="C39" t="s">
-        <v>501</v>
-      </c>
-      <c r="D39" s="8" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.25">
@@ -12173,13 +12332,13 @@
         <v>160</v>
       </c>
       <c r="B40" t="s">
+        <v>244</v>
+      </c>
+      <c r="C40" t="s">
+        <v>499</v>
+      </c>
+      <c r="D40" s="8" t="s">
         <v>245</v>
-      </c>
-      <c r="C40" t="s">
-        <v>501</v>
-      </c>
-      <c r="D40" s="8" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="41" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12190,10 +12349,10 @@
         <v>33</v>
       </c>
       <c r="C41" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D41" s="8" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
     </row>
     <row r="42" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12201,13 +12360,13 @@
         <v>182</v>
       </c>
       <c r="B42" t="s">
+        <v>247</v>
+      </c>
+      <c r="C42" t="s">
+        <v>499</v>
+      </c>
+      <c r="D42" s="8" t="s">
         <v>248</v>
-      </c>
-      <c r="C42" t="s">
-        <v>501</v>
-      </c>
-      <c r="D42" s="8" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.25">
@@ -12215,13 +12374,13 @@
         <v>183</v>
       </c>
       <c r="B43" t="s">
+        <v>249</v>
+      </c>
+      <c r="C43" t="s">
+        <v>499</v>
+      </c>
+      <c r="D43" s="8" t="s">
         <v>250</v>
-      </c>
-      <c r="C43" t="s">
-        <v>501</v>
-      </c>
-      <c r="D43" s="8" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.25">
@@ -12229,13 +12388,13 @@
         <v>192</v>
       </c>
       <c r="B44" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
       <c r="C44" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D44" s="8" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="45" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12243,13 +12402,13 @@
         <v>199</v>
       </c>
       <c r="B45" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C45" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D45" s="8" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="46" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12260,10 +12419,10 @@
         <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D46" s="8" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.25">
@@ -12274,10 +12433,10 @@
         <v>101</v>
       </c>
       <c r="C47" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D47" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.25">
@@ -12285,13 +12444,13 @@
         <v>203</v>
       </c>
       <c r="B48" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C48" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D48" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.25">
@@ -12299,13 +12458,13 @@
         <v>209</v>
       </c>
       <c r="B49" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C49" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D49" s="8" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.25">
@@ -12313,13 +12472,13 @@
         <v>214</v>
       </c>
       <c r="B50" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="C50" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D50" s="8" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.25">
@@ -12327,13 +12486,13 @@
         <v>232</v>
       </c>
       <c r="B51" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C51" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D51" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.25">
@@ -12341,13 +12500,13 @@
         <v>233</v>
       </c>
       <c r="B52" t="s">
+        <v>259</v>
+      </c>
+      <c r="C52" t="s">
+        <v>499</v>
+      </c>
+      <c r="D52" s="8" t="s">
         <v>260</v>
-      </c>
-      <c r="C52" t="s">
-        <v>501</v>
-      </c>
-      <c r="D52" s="8" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.25">
@@ -12355,13 +12514,13 @@
         <v>234</v>
       </c>
       <c r="B53" t="s">
+        <v>261</v>
+      </c>
+      <c r="C53" t="s">
+        <v>499</v>
+      </c>
+      <c r="D53" s="8" t="s">
         <v>262</v>
-      </c>
-      <c r="C53" t="s">
-        <v>501</v>
-      </c>
-      <c r="D53" s="8" t="s">
-        <v>263</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.25">
@@ -12369,13 +12528,13 @@
         <v>235</v>
       </c>
       <c r="B54" t="s">
+        <v>263</v>
+      </c>
+      <c r="C54" t="s">
+        <v>499</v>
+      </c>
+      <c r="D54" s="8" t="s">
         <v>264</v>
-      </c>
-      <c r="C54" t="s">
-        <v>501</v>
-      </c>
-      <c r="D54" s="8" t="s">
-        <v>265</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.25">
@@ -12383,13 +12542,13 @@
         <v>236</v>
       </c>
       <c r="B55" t="s">
+        <v>265</v>
+      </c>
+      <c r="C55" t="s">
+        <v>499</v>
+      </c>
+      <c r="D55" s="8" t="s">
         <v>266</v>
-      </c>
-      <c r="C55" t="s">
-        <v>501</v>
-      </c>
-      <c r="D55" s="8" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.25">
@@ -12397,13 +12556,13 @@
         <v>237</v>
       </c>
       <c r="B56" t="s">
+        <v>267</v>
+      </c>
+      <c r="C56" t="s">
+        <v>499</v>
+      </c>
+      <c r="D56" s="8" t="s">
         <v>268</v>
-      </c>
-      <c r="C56" t="s">
-        <v>501</v>
-      </c>
-      <c r="D56" s="8" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.25">
@@ -12411,13 +12570,13 @@
         <v>238</v>
       </c>
       <c r="B57" t="s">
+        <v>269</v>
+      </c>
+      <c r="C57" t="s">
+        <v>499</v>
+      </c>
+      <c r="D57" s="8" t="s">
         <v>270</v>
-      </c>
-      <c r="C57" t="s">
-        <v>501</v>
-      </c>
-      <c r="D57" s="8" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.25">
@@ -12425,13 +12584,13 @@
         <v>241</v>
       </c>
       <c r="B58" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" t="s">
+        <v>499</v>
+      </c>
+      <c r="D58" s="8" t="s">
         <v>272</v>
-      </c>
-      <c r="C58" t="s">
-        <v>501</v>
-      </c>
-      <c r="D58" s="8" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.25">
@@ -12439,13 +12598,13 @@
         <v>243</v>
       </c>
       <c r="B59" t="s">
+        <v>273</v>
+      </c>
+      <c r="C59" t="s">
+        <v>499</v>
+      </c>
+      <c r="D59" s="8" t="s">
         <v>274</v>
-      </c>
-      <c r="C59" t="s">
-        <v>501</v>
-      </c>
-      <c r="D59" s="8" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.25">
@@ -12453,13 +12612,13 @@
         <v>244</v>
       </c>
       <c r="B60" t="s">
+        <v>275</v>
+      </c>
+      <c r="C60" t="s">
+        <v>499</v>
+      </c>
+      <c r="D60" s="8" t="s">
         <v>276</v>
-      </c>
-      <c r="C60" t="s">
-        <v>501</v>
-      </c>
-      <c r="D60" s="8" t="s">
-        <v>277</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.25">
@@ -12467,13 +12626,13 @@
         <v>501</v>
       </c>
       <c r="B61" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C61" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D61" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.25">
@@ -12481,13 +12640,13 @@
         <v>502</v>
       </c>
       <c r="B62" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C62" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D62" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.25">
@@ -12495,13 +12654,13 @@
         <v>503</v>
       </c>
       <c r="B63" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C63" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.25">
@@ -12509,13 +12668,13 @@
         <v>504</v>
       </c>
       <c r="B64" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="C64" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D64" s="8" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.25">
@@ -12523,13 +12682,13 @@
         <v>505</v>
       </c>
       <c r="B65" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C65" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D65" s="8" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
     </row>
     <row r="66" spans="1:4" ht="30" x14ac:dyDescent="0.25">
@@ -12540,10 +12699,10 @@
         <v>50</v>
       </c>
       <c r="C66" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D66" s="17" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.25">
@@ -12551,13 +12710,13 @@
         <v>507</v>
       </c>
       <c r="B67" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C67" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D67" s="8" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.25">
@@ -12568,10 +12727,10 @@
         <v>53</v>
       </c>
       <c r="C68" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D68" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.25">
@@ -12579,13 +12738,13 @@
         <v>509</v>
       </c>
       <c r="B69" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="C69" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D69" s="8" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.25">
@@ -12593,1175 +12752,1237 @@
         <v>510</v>
       </c>
       <c r="B70" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="C70" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D70" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A71" s="10" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="B71" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C71" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D71" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B72" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="C72" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D72" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A73" s="10" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B73" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="C73" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D73" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="B74" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C74" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D74" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A75" s="10" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B75" t="s">
         <v>140</v>
       </c>
       <c r="C75" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D75" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B76" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="C76" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D76" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A77" s="10" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="B77" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C77" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D77" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B78" t="s">
         <v>86</v>
       </c>
       <c r="C78" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D78" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A79" s="10" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B79" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C79" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D79" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B80" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C80" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D80" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" s="10" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B81" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C81" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D81" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B82" t="s">
+        <v>488</v>
+      </c>
+      <c r="C82" t="s">
         <v>490</v>
       </c>
-      <c r="C82" t="s">
-        <v>492</v>
-      </c>
       <c r="D82" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" s="10" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B83" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="C83" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D83" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B84" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C84" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D84" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" s="10" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B85" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C85" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D85" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B86" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="C86" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D86" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" s="10" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B87" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="C87" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D87" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B88" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C88" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D88" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" s="10" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B89" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C89" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D89" s="8" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B90" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C90" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D90" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" s="10" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B91" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C91" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D91" s="8" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B92" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="C92" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D92" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" s="10" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B93" t="s">
         <v>101</v>
       </c>
       <c r="C93" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D93" s="8" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B94" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C94" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D94" s="8" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A95" s="10" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="B95" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C95" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D95" s="8" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="B96" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C96" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D96" s="8" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A97" s="10" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B97" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C97" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D97" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="B98" t="s">
         <v>58</v>
       </c>
       <c r="C98" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D98" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A99" s="10" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="B99" t="s">
         <v>62</v>
       </c>
       <c r="C99" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D99" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="B100" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C100" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D100" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A101" s="10" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B101" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C101" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D101" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B102" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C102" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D102" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A103" s="10" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B103" t="s">
         <v>19</v>
       </c>
       <c r="C103" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D103" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B104" t="s">
         <v>140</v>
       </c>
       <c r="C104" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D104" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A105" s="10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="B105" t="s">
         <v>86</v>
       </c>
       <c r="C105" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D105" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B106" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C106" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D106" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A107" s="10" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="B107" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C107" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D107" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B108" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C108" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D108" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A109" s="10" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B109" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C109" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D109" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="B110" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C110" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D110" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A111" s="10" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="B111" t="s">
         <v>33</v>
       </c>
       <c r="C111" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D111" s="8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B112" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C112" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D112" s="8" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="113" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A113" s="10" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B113" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C113" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D113" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="114" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="B114" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C114" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D114" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="115" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A115" s="10" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="B115" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="C115" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D115" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="116" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="B116" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C116" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D116" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="117" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A117" s="10" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="B117" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="C117" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D117" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="118" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="B118" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="C118" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D118" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="119" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A119" s="10" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="B119" t="s">
         <v>140</v>
       </c>
       <c r="C119" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D119" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="120" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="B120" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="C120" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D120" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="121" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A121" s="10" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="B121" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="C121" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D121" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="122" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="B122" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="C122" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D122" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="123" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A123" s="10" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="B123" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="C123" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D123" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="124" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B124" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="C124" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D124" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="125" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A125" s="10" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="B125" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C125" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D125" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="126" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B126" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="C126" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D126" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="127" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A127" s="10" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="B127" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C127" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D127" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="128" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="B128" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="C128" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D128" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="129" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A129" s="10" t="s">
+        <v>424</v>
+      </c>
+      <c r="B129" t="s">
         <v>426</v>
       </c>
-      <c r="B129" t="s">
-        <v>428</v>
-      </c>
       <c r="C129" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D129" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="130" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="B130" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C130" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="D130" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A131" s="10" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B131" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="C131" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D131" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="132" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="B132" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="C132" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D132" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A133" s="10" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="B133" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="C133" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D133" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
     </row>
     <row r="134" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
+        <v>480</v>
+      </c>
+      <c r="B134" t="s">
         <v>482</v>
       </c>
-      <c r="B134" t="s">
-        <v>484</v>
-      </c>
       <c r="C134" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D134" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
     </row>
     <row r="135" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A135" s="10" t="s">
+        <v>521</v>
+      </c>
+      <c r="B135" t="s">
+        <v>522</v>
+      </c>
+      <c r="C135" t="s">
+        <v>499</v>
+      </c>
+      <c r="D135" t="s">
         <v>523</v>
-      </c>
-      <c r="B135" t="s">
-        <v>524</v>
-      </c>
-      <c r="C135" t="s">
-        <v>501</v>
-      </c>
-      <c r="D135" t="s">
-        <v>525</v>
       </c>
     </row>
     <row r="136" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
+        <v>539</v>
+      </c>
+      <c r="B136" t="s">
         <v>541</v>
       </c>
-      <c r="B136" t="s">
-        <v>543</v>
-      </c>
       <c r="C136" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D136" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
     </row>
     <row r="137" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A137" s="10" t="s">
+        <v>538</v>
+      </c>
+      <c r="B137" t="s">
+        <v>488</v>
+      </c>
+      <c r="C137" t="s">
+        <v>490</v>
+      </c>
+      <c r="D137" t="s">
         <v>540</v>
-      </c>
-      <c r="B137" t="s">
-        <v>490</v>
-      </c>
-      <c r="C137" t="s">
-        <v>492</v>
-      </c>
-      <c r="D137" t="s">
-        <v>542</v>
       </c>
     </row>
     <row r="138" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
+        <v>546</v>
+      </c>
+      <c r="B138" t="s">
         <v>548</v>
       </c>
-      <c r="B138" t="s">
-        <v>550</v>
-      </c>
       <c r="C138" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D138" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
     </row>
     <row r="139" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A139" s="10" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="B139" t="s">
+        <v>488</v>
+      </c>
+      <c r="C139" t="s">
         <v>490</v>
       </c>
-      <c r="C139" t="s">
-        <v>492</v>
-      </c>
       <c r="D139" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
     </row>
     <row r="140" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="B140" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="C140" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D140" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
     </row>
     <row r="141" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A141" s="10" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B141" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="C141" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D141" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="142" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
+        <v>553</v>
+      </c>
+      <c r="B142" t="s">
+        <v>430</v>
+      </c>
+      <c r="C142" t="s">
+        <v>490</v>
+      </c>
+      <c r="D142" t="s">
         <v>555</v>
-      </c>
-      <c r="B142" t="s">
-        <v>432</v>
-      </c>
-      <c r="C142" t="s">
-        <v>492</v>
-      </c>
-      <c r="D142" t="s">
-        <v>557</v>
       </c>
     </row>
     <row r="143" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A143" s="10" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="B143" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="C143" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D143" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="144" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
+        <v>566</v>
+      </c>
+      <c r="B144" t="s">
+        <v>567</v>
+      </c>
+      <c r="C144" t="s">
+        <v>499</v>
+      </c>
+      <c r="D144" t="s">
         <v>568</v>
       </c>
-      <c r="B144" t="s">
-        <v>569</v>
-      </c>
-      <c r="C144" t="s">
-        <v>501</v>
-      </c>
-      <c r="D144" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A145" s="10" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="B145" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C145" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D145" t="s">
-        <v>615</v>
-      </c>
-    </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.25">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="B146" t="s">
         <v>140</v>
       </c>
       <c r="C146" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D146" s="25" t="s">
-        <v>632</v>
-      </c>
-    </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.25">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A147" s="10" t="s">
+        <v>636</v>
+      </c>
+      <c r="B147" t="s">
+        <v>637</v>
+      </c>
+      <c r="C147" t="s">
+        <v>499</v>
+      </c>
+      <c r="D147" t="s">
         <v>638</v>
       </c>
-      <c r="B147" t="s">
-        <v>639</v>
-      </c>
-      <c r="C147" t="s">
-        <v>501</v>
-      </c>
-      <c r="D147" t="s">
-        <v>640</v>
-      </c>
-    </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B148" t="s">
+        <v>668</v>
+      </c>
+      <c r="C148" t="s">
+        <v>499</v>
+      </c>
+      <c r="D148" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A149" s="10" t="s">
+        <v>669</v>
+      </c>
+      <c r="B149" t="s">
+        <v>668</v>
+      </c>
+      <c r="C149" t="s">
+        <v>499</v>
+      </c>
+      <c r="D149" t="s">
         <v>670</v>
       </c>
-      <c r="C148" t="s">
-        <v>501</v>
-      </c>
-      <c r="D148" t="s">
-        <v>665</v>
-      </c>
-    </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A149" s="10" t="s">
-        <v>671</v>
-      </c>
-      <c r="B149" t="s">
-        <v>670</v>
-      </c>
-      <c r="C149" t="s">
-        <v>501</v>
-      </c>
-      <c r="D149" t="s">
-        <v>672</v>
-      </c>
-    </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
+        <v>677</v>
+      </c>
+      <c r="B150" t="s">
+        <v>668</v>
+      </c>
+      <c r="C150" t="s">
+        <v>499</v>
+      </c>
+      <c r="D150" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A151" s="10" t="s">
+        <v>678</v>
+      </c>
+      <c r="B151" t="s">
+        <v>680</v>
+      </c>
+      <c r="C151" t="s">
+        <v>499</v>
+      </c>
+      <c r="D151" t="s">
         <v>679</v>
       </c>
-      <c r="B150" t="s">
-        <v>670</v>
-      </c>
-      <c r="C150" t="s">
-        <v>501</v>
-      </c>
-      <c r="D150" t="s">
-        <v>678</v>
-      </c>
-    </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A151" s="10" t="s">
-        <v>680</v>
-      </c>
-      <c r="B151" t="s">
-        <v>682</v>
-      </c>
-      <c r="C151" t="s">
-        <v>501</v>
-      </c>
-      <c r="D151" t="s">
-        <v>681</v>
-      </c>
-    </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.25">
+    </row>
+    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="B152" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C152" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D152" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.25">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A153" s="10" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="B153" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="C153" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D153" t="s">
-        <v>848</v>
+        <v>845</v>
+      </c>
+    </row>
+    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A154" s="10" t="s">
+        <v>856</v>
+      </c>
+      <c r="B154" t="s">
+        <v>338</v>
+      </c>
+      <c r="C154" t="s">
+        <v>499</v>
+      </c>
+      <c r="D154" t="s">
+        <v>858</v>
+      </c>
+      <c r="E154" s="30" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A155" s="10" t="s">
+        <v>857</v>
+      </c>
+      <c r="B155" t="s">
+        <v>254</v>
+      </c>
+      <c r="C155" t="s">
+        <v>499</v>
+      </c>
+      <c r="D155" t="s">
+        <v>859</v>
+      </c>
+      <c r="E155" s="30" t="s">
+        <v>860</v>
+      </c>
+    </row>
+    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A156" s="10" t="s">
+        <v>867</v>
+      </c>
+      <c r="B156" t="s">
+        <v>863</v>
+      </c>
+      <c r="C156" t="s">
+        <v>499</v>
+      </c>
+      <c r="D156" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A157" s="10" t="s">
+        <v>866</v>
+      </c>
+      <c r="B157" t="s">
+        <v>868</v>
+      </c>
+      <c r="C157" t="s">
+        <v>499</v>
+      </c>
+      <c r="D157" t="s">
+        <v>865</v>
       </c>
     </row>
   </sheetData>
@@ -13818,7 +14039,7 @@
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B3">
         <v>203</v>
@@ -13959,7 +14180,7 @@
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="B11">
         <v>311</v>
@@ -13967,7 +14188,7 @@
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="B12">
         <v>312</v>
@@ -13999,7 +14220,7 @@
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="B16">
         <v>317</v>
@@ -14111,7 +14332,7 @@
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B30">
         <v>331</v>
@@ -14119,7 +14340,7 @@
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="B31">
         <v>332</v>
@@ -14127,7 +14348,7 @@
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B32">
         <v>333</v>
@@ -14153,50 +14374,50 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="16" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="B2" s="10" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="10" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="B3" s="10" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="B4" s="10" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="10" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="B5" s="10" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="10" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>
